--- a/datos/bbdd_ligamx.xlsx
+++ b/datos/bbdd_ligamx.xlsx
@@ -831,77 +831,77 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
         <v>13</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="S4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="T4" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="U4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W4" s="2" t="n">
         <v>9</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z4" s="2" t="n">
         <v>1</v>
@@ -929,77 +929,77 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q5" s="2" t="n">
         <v>13</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W5" s="2" t="n">
         <v>9</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>1</v>
@@ -1125,29 +1125,29 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>
@@ -1156,55 +1156,55 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="U7" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="V7" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W7" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="X7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y7" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1223,32 +1223,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>01:07</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -1260,46 +1260,46 @@
         <v>1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W8" s="2" t="n">
         <v>14</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" s="2" t="n">
         <v>0</v>
@@ -1321,29 +1321,29 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>0</v>
@@ -1352,55 +1352,55 @@
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W9" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X9" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="U9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="W9" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="X9" s="2" t="n">
-        <v>13</v>
-      </c>
       <c r="Y9" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1419,32 +1419,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>01:07</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -1456,46 +1456,46 @@
         <v>1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q10" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="R10" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="T10" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W10" s="2" t="n">
         <v>14</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="2" t="n">
         <v>0</v>
@@ -2203,86 +2203,86 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P18" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W18" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Y18" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Z18" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -2301,86 +2301,86 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P19" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="R19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="S19" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="T19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="V19" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="W19" s="2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="X19" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y19" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Z19" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3281,83 +3281,83 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="R29" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="S29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T29" s="2" t="n">
+      <c r="V29" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="U29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V29" s="2" t="n">
-        <v>16</v>
-      </c>
       <c r="W29" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="X29" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Y29" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Z29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" s="2" t="n">
         <v>0</v>
@@ -3477,83 +3477,83 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Atlante</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R31" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="W31" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X31" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="S31" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="T31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U31" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="V31" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="W31" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="X31" s="2" t="n">
-        <v>7</v>
-      </c>
       <c r="Y31" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Z31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB31" s="2" t="n">
         <v>0</v>
@@ -3575,86 +3575,86 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P32" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W32" s="2" t="n">
         <v>13</v>
       </c>
       <c r="X32" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y32" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Z32" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3673,29 +3673,29 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>01:10</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0</v>
@@ -3707,52 +3707,52 @@
         <v>0</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R33" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="S33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="V33" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="W33" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="X33" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Z33" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3771,86 +3771,86 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P34" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q34" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="R34" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="R34" s="2" t="n">
-        <v>14</v>
-      </c>
       <c r="S34" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V34" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="U34" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="V34" s="2" t="n">
-        <v>6</v>
       </c>
       <c r="W34" s="2" t="n">
         <v>13</v>
       </c>
       <c r="X34" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Y34" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Z34" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -3869,29 +3869,29 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>01:10</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0</v>
@@ -3903,52 +3903,52 @@
         <v>0</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="R35" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W35" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="S35" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U35" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="V35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W35" s="2" t="n">
+      <c r="X35" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="X35" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="Y35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Z35" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -3967,86 +3967,86 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:06</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O36" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="S36" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T36" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V36" s="2" t="n">
         <v>3</v>
       </c>
       <c r="W36" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X36" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="X36" s="2" t="n">
-        <v>14</v>
-      </c>
       <c r="Y36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -4065,86 +4065,86 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O37" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="R37" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="S37" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T37" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V37" s="2" t="n">
         <v>3</v>
       </c>
       <c r="W37" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="X37" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -4555,77 +4555,77 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I42" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q42" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R42" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="R42" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="S42" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T42" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V42" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W42" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y42" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z42" s="2" t="n">
         <v>1</v>
@@ -4653,77 +4653,77 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P43" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N43" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="O43" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P43" s="2" t="n">
+      <c r="Q43" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S43" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="Q43" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="R43" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="S43" s="2" t="n">
+      <c r="T43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V43" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W43" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X43" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="T43" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U43" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="V43" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W43" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="X43" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="Y43" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="2" t="n">
         <v>1</v>
@@ -5045,86 +5045,86 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R47" s="2" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="S47" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T47" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U47" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V47" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W47" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="X47" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y47" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z47" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -5143,41 +5143,41 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" s="2" t="n">
         <v>0</v>
@@ -5189,37 +5189,37 @@
         <v>2</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R48" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S48" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T48" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U48" s="2" t="n">
         <v>3</v>
       </c>
       <c r="V48" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W48" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="X48" s="2" t="n">
         <v>10</v>
       </c>
       <c r="Y48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AA48" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB48" s="2" t="n">
         <v>1</v>
@@ -5251,19 +5251,19 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Atlante</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0</v>
@@ -5272,55 +5272,55 @@
         <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P49" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R49" s="2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S49" s="2" t="n">
         <v>4</v>
       </c>
       <c r="T49" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U49" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W49" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X49" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y49" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="U49" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V49" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="W49" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="X49" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y49" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="Z49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -6025,22 +6025,22 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Atlante</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
@@ -6056,49 +6056,49 @@
         <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P57" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q57" s="2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R57" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="S57" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T57" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U57" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V57" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W57" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="X57" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Y57" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z57" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA57" s="2" t="n">
         <v>0</v>
@@ -6123,80 +6123,80 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O58" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q58" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R58" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S58" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T58" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U58" s="2" t="n">
         <v>3</v>
       </c>
       <c r="V58" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W58" s="2" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="X58" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z58" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA58" s="2" t="n">
         <v>0</v>
@@ -6221,80 +6221,80 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N59" s="2" t="n">
         <v>2</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P59" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q59" s="2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="R59" s="2" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="S59" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T59" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U59" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V59" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W59" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="X59" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y59" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA59" s="2" t="n">
         <v>0</v>
@@ -8181,77 +8181,77 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P79" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q79" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R79" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="S79" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T79" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U79" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V79" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W79" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X79" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="V79" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W79" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="X79" s="2" t="n">
-        <v>13</v>
-      </c>
       <c r="Y79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z79" s="2" t="n">
         <v>0</v>
@@ -8279,35 +8279,35 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H80" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I80" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -8316,43 +8316,43 @@
         <v>1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P80" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q80" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="R80" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="R80" s="2" t="n">
-        <v>13</v>
-      </c>
       <c r="S80" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T80" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U80" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V80" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W80" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X80" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA80" s="2" t="n">
         <v>0</v>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Mazatlan</t>
         </is>
       </c>
       <c r="H81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -8414,43 +8414,43 @@
         <v>1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P81" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q81" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S81" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="R81" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="S81" s="2" t="n">
-        <v>3</v>
       </c>
       <c r="T81" s="2" t="n">
         <v>6</v>
       </c>
       <c r="U81" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V81" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W81" s="2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="X81" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Y81" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z81" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA81" s="2" t="n">
         <v>0</v>
@@ -8475,80 +8475,80 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Mazatlan</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="H82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N82" s="2" t="n">
         <v>2</v>
       </c>
       <c r="O82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P82" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q82" s="2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="R82" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="S82" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T82" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U82" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V82" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W82" s="2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="X82" s="2" t="n">
         <v>13</v>
       </c>
       <c r="Y82" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA82" s="2" t="n">
         <v>0</v>
@@ -8573,29 +8573,29 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>03:06</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="H83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0</v>
@@ -8604,55 +8604,55 @@
         <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P83" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q83" s="2" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="R83" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="S83" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T83" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U83" s="2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="V83" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W83" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="X83" s="2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="Y83" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z83" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -8671,80 +8671,80 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P84" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q84" s="2" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="R84" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="S84" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T84" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U84" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V84" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W84" s="2" t="n">
         <v>14</v>
       </c>
       <c r="X84" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y84" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z84" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA84" s="2" t="n">
         <v>1</v>
@@ -8965,26 +8965,26 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="H87" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I87" s="2" t="n">
         <v>1</v>
@@ -8993,7 +8993,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>1</v>
@@ -9005,46 +9005,46 @@
         <v>1</v>
       </c>
       <c r="O87" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P87" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q87" s="2" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="R87" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S87" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="T87" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U87" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W87" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X87" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y87" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z87" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T87" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U87" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="V87" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="W87" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="X87" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y87" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z87" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="AA87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -9357,32 +9357,32 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="H91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -9391,49 +9391,49 @@
         <v>0</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P91" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R91" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S91" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T91" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U91" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V91" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W91" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X91" s="2" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="Y91" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z91" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB91" s="2" t="n">
         <v>0</v>
@@ -9553,32 +9553,32 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:06</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -9587,49 +9587,49 @@
         <v>0</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P93" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q93" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R93" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S93" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T93" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U93" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V93" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W93" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X93" s="2" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="Y93" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z93" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB93" s="2" t="n">
         <v>0</v>
@@ -9651,80 +9651,80 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O94" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P94" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q94" s="2" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="R94" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="S94" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T94" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U94" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V94" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T94" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="U94" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="V94" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="W94" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X94" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y94" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z94" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA94" s="2" t="n">
         <v>0</v>
@@ -9847,80 +9847,80 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="H96" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O96" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P96" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q96" s="2" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="R96" s="2" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="S96" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T96" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U96" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V96" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W96" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X96" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y96" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z96" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA96" s="2" t="n">
         <v>0</v>
@@ -9945,86 +9945,86 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:06</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H97" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O97" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P97" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q97" s="2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="R97" s="2" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="S97" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T97" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U97" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V97" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W97" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="X97" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y97" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z97" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -10141,86 +10141,86 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="H99" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O99" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P99" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q99" s="2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="R99" s="2" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="S99" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T99" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U99" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V99" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="W99" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="X99" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y99" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z99" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -10239,86 +10239,86 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>01:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H100" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O100" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P100" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q100" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R100" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S100" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T100" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U100" s="2" t="n">
         <v>6</v>
       </c>
       <c r="V100" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W100" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="X100" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y100" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z100" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -10337,86 +10337,86 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Mazatlan</t>
         </is>
       </c>
       <c r="H101" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P101" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q101" s="2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="R101" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="S101" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T101" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U101" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V101" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W101" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="X101" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="T101" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U101" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="V101" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="W101" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="X101" s="2" t="n">
-        <v>14</v>
-      </c>
       <c r="Y101" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z101" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -10435,77 +10435,77 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>01:10</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="H102" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O102" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P102" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q102" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R102" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S102" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T102" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U102" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V102" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W102" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="R102" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="S102" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="T102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U102" s="2" t="n">
+      <c r="X102" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y102" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="V102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="X102" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y102" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="Z102" s="2" t="n">
         <v>2</v>
@@ -10533,86 +10533,86 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Mazatlan</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="H103" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P103" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q103" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="R103" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="S103" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T103" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U103" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T103" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U103" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="V103" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W103" s="2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="X103" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Y103" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z103" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -10631,86 +10631,86 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="H104" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O104" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q104" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="R104" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S104" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U104" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="Q104" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="R104" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="S104" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T104" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="U104" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="V104" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W104" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="X104" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y104" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Z104" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -10837,67 +10837,67 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Mazatlan</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P106" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q106" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="R106" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="S106" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T106" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V106" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W106" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="S106" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T106" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U106" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V106" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="W106" s="2" t="n">
-        <v>16</v>
-      </c>
       <c r="X106" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y106" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z106" s="2" t="n">
         <v>2</v>
@@ -10925,86 +10925,86 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:06</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O107" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P107" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q107" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R107" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="S107" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T107" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U107" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V107" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="S107" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="T107" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U107" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V107" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="W107" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="X107" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="X107" s="2" t="n">
-        <v>17</v>
-      </c>
       <c r="Y107" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z107" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB107" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -11033,76 +11033,76 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H108" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O108" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P108" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I108" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J108" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K108" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L108" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="O108" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P108" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="Q108" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R108" s="2" t="n">
         <v>8</v>
       </c>
       <c r="S108" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T108" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U108" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V108" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W108" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X108" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Y108" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z108" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB108" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -11121,83 +11121,83 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Mazatlan</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="H109" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O109" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P109" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q109" s="2" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="R109" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="S109" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T109" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U109" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V109" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W109" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X109" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y109" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z109" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB109" s="2" t="n">
         <v>0</v>
@@ -11523,31 +11523,31 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H113" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N113" s="2" t="n">
         <v>1</v>
@@ -11559,40 +11559,40 @@
         <v>2</v>
       </c>
       <c r="Q113" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R113" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="S113" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T113" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="U113" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V113" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W113" s="2" t="n">
         <v>15</v>
       </c>
       <c r="X113" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Y113" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z113" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -11621,31 +11621,31 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H114" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N114" s="2" t="n">
         <v>1</v>
@@ -11657,40 +11657,40 @@
         <v>2</v>
       </c>
       <c r="Q114" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R114" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="S114" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T114" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U114" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="U114" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="V114" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="W114" s="2" t="n">
         <v>15</v>
       </c>
       <c r="X114" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Y114" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z114" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -12101,29 +12101,29 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>03:07</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H119" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>1</v>
@@ -12132,49 +12132,49 @@
         <v>0</v>
       </c>
       <c r="L119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P119" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q119" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R119" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="S119" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T119" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U119" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V119" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W119" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X119" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y119" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z119" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA119" s="2" t="n">
         <v>0</v>
@@ -12199,22 +12199,22 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>03:07</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H120" s="2" t="n">
@@ -12245,34 +12245,34 @@
         <v>1</v>
       </c>
       <c r="Q120" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R120" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S120" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T120" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U120" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="S120" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T120" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U120" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="V120" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W120" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X120" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="Y120" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z120" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA120" s="2" t="n">
         <v>0</v>
@@ -12297,29 +12297,29 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="H121" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>1</v>
@@ -12328,49 +12328,49 @@
         <v>0</v>
       </c>
       <c r="L121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P121" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q121" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R121" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S121" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T121" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U121" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V121" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W121" s="2" t="n">
         <v>17</v>
       </c>
       <c r="X121" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y121" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z121" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA121" s="2" t="n">
         <v>0</v>
@@ -12591,83 +12591,83 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="H124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L124" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N124" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O124" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P124" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q124" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="R124" s="2" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="S124" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T124" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U124" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V124" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W124" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="U124" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V124" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="W124" s="2" t="n">
-        <v>13</v>
-      </c>
       <c r="X124" s="2" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="Y124" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z124" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB124" s="2" t="n">
         <v>0</v>
@@ -12689,83 +12689,83 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:06</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H125" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L125" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N125" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O125" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P125" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q125" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="R125" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="S125" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T125" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U125" s="2" t="n">
         <v>3</v>
       </c>
       <c r="V125" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W125" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="X125" s="2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="Y125" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z125" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA125" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB125" s="2" t="n">
         <v>0</v>
@@ -13767,83 +13767,83 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="H136" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J136" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L136" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O136" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P136" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q136" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R136" s="2" t="n">
         <v>11</v>
       </c>
       <c r="S136" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T136" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U136" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V136" s="2" t="n">
         <v>5</v>
       </c>
       <c r="W136" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X136" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y136" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z136" s="2" t="n">
         <v>4</v>
       </c>
       <c r="AA136" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB136" s="2" t="n">
         <v>0</v>
@@ -13865,83 +13865,83 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H137" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J137" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L137" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M137" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N137" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O137" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P137" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q137" s="2" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="R137" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S137" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T137" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="T137" s="2" t="n">
-        <v>4</v>
       </c>
       <c r="U137" s="2" t="n">
         <v>9</v>
       </c>
       <c r="V137" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W137" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="X137" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y137" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z137" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA137" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB137" s="2" t="n">
         <v>0</v>
@@ -13963,83 +13963,83 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="H138" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M138" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P138" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q138" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="R138" s="2" t="n">
         <v>10</v>
       </c>
       <c r="S138" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T138" s="2" t="n">
         <v>4</v>
       </c>
       <c r="U138" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V138" s="2" t="n">
         <v>4</v>
       </c>
       <c r="W138" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X138" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y138" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z138" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB138" s="2" t="n">
         <v>0</v>
@@ -14061,77 +14061,77 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H139" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K139" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L139" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O139" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P139" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q139" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R139" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S139" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T139" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U139" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V139" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W139" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="X139" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y139" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z139" s="2" t="n">
         <v>3</v>
@@ -14159,83 +14159,83 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="H140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O140" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P140" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q140" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R140" s="2" t="n">
         <v>11</v>
       </c>
       <c r="S140" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T140" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U140" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V140" s="2" t="n">
         <v>5</v>
       </c>
       <c r="W140" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="X140" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Y140" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z140" s="2" t="n">
         <v>4</v>
       </c>
       <c r="AA140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB140" s="2" t="n">
         <v>0</v>
@@ -15237,22 +15237,22 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H151" s="2" t="n">
@@ -15268,55 +15268,55 @@
         <v>0</v>
       </c>
       <c r="L151" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P151" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q151" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R151" s="2" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="S151" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T151" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U151" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V151" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="U151" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="V151" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="W151" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="X151" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y151" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z151" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA151" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB151" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -15335,86 +15335,86 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="H152" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L152" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O152" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P152" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q152" s="2" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="R152" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S152" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T152" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V152" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W152" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="S152" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T152" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U152" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V152" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="W152" s="2" t="n">
-        <v>18</v>
-      </c>
       <c r="X152" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y152" s="2" t="n">
         <v>4</v>
       </c>
       <c r="Z152" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA152" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB152" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -15433,83 +15433,83 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="H153" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L153" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N153" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O153" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P153" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q153" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="R153" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="S153" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="U153" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="V153" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W153" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="X153" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Y153" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z153" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA153" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB153" s="2" t="n">
         <v>0</v>
@@ -15531,35 +15531,35 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H154" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I154" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L154" s="2" t="n">
         <v>0</v>
@@ -15568,40 +15568,40 @@
         <v>0</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O154" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P154" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q154" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="R154" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="S154" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="T154" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U154" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V154" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W154" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X154" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Y154" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z154" s="2" t="n">
         <v>2</v>
@@ -15610,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="AB154" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -15639,76 +15639,76 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H155" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J155" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L155" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M155" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O155" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P155" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q155" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="R155" s="2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="S155" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="T155" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U155" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V155" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W155" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="X155" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y155" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Z155" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA155" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB155" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -16413,83 +16413,83 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="H163" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J163" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L163" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M163" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O163" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P163" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q163" s="2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R163" s="2" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="S163" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T163" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U163" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V163" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W163" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X163" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y163" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z163" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA163" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB163" s="2" t="n">
         <v>0</v>
@@ -16511,83 +16511,83 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H164" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J164" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L164" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O164" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P164" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q164" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="R164" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="R164" s="2" t="n">
-        <v>12</v>
-      </c>
       <c r="S164" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T164" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U164" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="U164" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="V164" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W164" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X164" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y164" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z164" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA164" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB164" s="2" t="n">
         <v>0</v>
@@ -16609,35 +16609,35 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Mazatlan</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="H165" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I165" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L165" s="2" t="n">
         <v>0</v>
@@ -16646,43 +16646,43 @@
         <v>0</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O165" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P165" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q165" s="2" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="R165" s="2" t="n">
         <v>8</v>
       </c>
       <c r="S165" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T165" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U165" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V165" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W165" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X165" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Y165" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z165" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA165" s="2" t="n">
         <v>0</v>
@@ -16707,35 +16707,35 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Mazatlan</t>
         </is>
       </c>
       <c r="H166" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I166" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L166" s="2" t="n">
         <v>0</v>
@@ -16744,43 +16744,43 @@
         <v>0</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O166" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P166" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q166" s="2" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="R166" s="2" t="n">
         <v>8</v>
       </c>
       <c r="S166" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T166" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U166" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V166" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W166" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X166" s="2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Y166" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z166" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA166" s="2" t="n">
         <v>0</v>
@@ -16903,77 +16903,77 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:06</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Mazatlan</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H168" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L168" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M168" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O168" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P168" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q168" s="2" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="R168" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="S168" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T168" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U168" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V168" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="S168" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="T168" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U168" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="V168" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="W168" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X168" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y168" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z168" s="2" t="n">
         <v>2</v>
@@ -17001,77 +17001,77 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>Mazatlan</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="H169" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L169" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O169" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P169" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q169" s="2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="R169" s="2" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="S169" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T169" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U169" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="U169" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="V169" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W169" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X169" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y169" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z169" s="2" t="n">
         <v>2</v>
@@ -17099,26 +17099,26 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="H170" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I170" s="2" t="n">
         <v>0</v>
@@ -17127,7 +17127,7 @@
         <v>0</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L170" s="2" t="n">
         <v>0</v>
@@ -17139,43 +17139,43 @@
         <v>0</v>
       </c>
       <c r="O170" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P170" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q170" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="R170" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S170" s="2" t="n">
         <v>3</v>
       </c>
       <c r="T170" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U170" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V170" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W170" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="X170" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y170" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z170" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA170" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB170" s="2" t="n">
         <v>0</v>
@@ -17393,26 +17393,26 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H173" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I173" s="2" t="n">
         <v>0</v>
@@ -17421,7 +17421,7 @@
         <v>0</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L173" s="2" t="n">
         <v>0</v>
@@ -17433,43 +17433,43 @@
         <v>0</v>
       </c>
       <c r="O173" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P173" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q173" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="R173" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="S173" s="2" t="n">
         <v>3</v>
       </c>
       <c r="T173" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U173" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V173" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W173" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="X173" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y173" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z173" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA173" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB173" s="2" t="n">
         <v>0</v>
@@ -18079,22 +18079,22 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="H180" s="2" t="n">
@@ -18110,55 +18110,55 @@
         <v>0</v>
       </c>
       <c r="L180" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M180" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O180" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P180" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q180" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R180" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S180" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T180" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U180" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V180" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W180" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="U180" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="V180" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="W180" s="2" t="n">
-        <v>9</v>
-      </c>
       <c r="X180" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Y180" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z180" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA180" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB180" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -18177,32 +18177,32 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="H181" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K181" s="2" t="n">
         <v>1</v>
@@ -18211,52 +18211,52 @@
         <v>0</v>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O181" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P181" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q181" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R181" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S181" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T181" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U181" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V181" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W181" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X181" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="R181" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="S181" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T181" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U181" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V181" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W181" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="X181" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="Y181" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z181" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA181" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB181" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -18275,32 +18275,32 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H182" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K182" s="2" t="n">
         <v>1</v>
@@ -18309,52 +18309,52 @@
         <v>0</v>
       </c>
       <c r="M182" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O182" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P182" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q182" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="R182" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="S182" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T182" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U182" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V182" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W182" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="R182" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="S182" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="T182" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U182" s="2" t="n">
+      <c r="X182" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="V182" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="W182" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="X182" s="2" t="n">
-        <v>9</v>
-      </c>
       <c r="Y182" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z182" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA182" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB182" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -18373,22 +18373,22 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H183" s="2" t="n">
@@ -18404,55 +18404,55 @@
         <v>0</v>
       </c>
       <c r="L183" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O183" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P183" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q183" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R183" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S183" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T183" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T183" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="U183" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V183" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="W183" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X183" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="V183" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W183" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="X183" s="2" t="n">
-        <v>12</v>
-      </c>
       <c r="Y183" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z183" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA183" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB183" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -18961,35 +18961,35 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>03:05</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H189" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I189" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K189" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L189" s="2" t="n">
         <v>1</v>
@@ -18998,43 +18998,43 @@
         <v>0</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O189" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P189" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q189" s="2" t="n">
         <v>11</v>
       </c>
       <c r="R189" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="S189" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T189" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U189" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V189" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W189" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="X189" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y189" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z189" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA189" s="2" t="n">
         <v>0</v>
@@ -19069,76 +19069,76 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="H190" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K190" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L190" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M190" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O190" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P190" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q190" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R190" s="2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="S190" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T190" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U190" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V190" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W190" s="2" t="n">
         <v>15</v>
       </c>
       <c r="X190" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Y190" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z190" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA190" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB190" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -19157,60 +19157,60 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="H191" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J191" s="2" t="n">
         <v>2</v>
       </c>
       <c r="K191" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L191" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M191" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O191" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P191" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q191" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R191" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S191" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Q191" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="R191" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="S191" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="T191" s="2" t="n">
         <v>1</v>
       </c>
@@ -19218,16 +19218,16 @@
         <v>4</v>
       </c>
       <c r="V191" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W191" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="X191" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y191" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z191" s="2" t="n">
         <v>2</v>
@@ -19236,7 +19236,7 @@
         <v>0</v>
       </c>
       <c r="AB191" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192">
@@ -19255,68 +19255,68 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:05</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H192" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I192" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K192" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L192" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N192" s="2" t="n">
         <v>2</v>
       </c>
       <c r="O192" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P192" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q192" s="2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="R192" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="S192" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T192" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U192" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="S192" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="T192" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U192" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="V192" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W192" s="2" t="n">
         <v>9</v>
@@ -19325,16 +19325,16 @@
         <v>10</v>
       </c>
       <c r="Y192" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z192" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA192" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB192" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -19353,71 +19353,71 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="H193" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K193" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L193" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M193" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O193" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P193" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q193" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="R193" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="S193" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T193" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="Q193" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="R193" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="S193" s="2" t="n">
+      <c r="U193" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T193" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="U193" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="V193" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W193" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X193" s="2" t="n">
         <v>13</v>
@@ -19426,7 +19426,7 @@
         <v>3</v>
       </c>
       <c r="Z193" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA193" s="2" t="n">
         <v>0</v>
@@ -20539,28 +20539,28 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="H205" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K205" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L205" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M205" s="2" t="n">
         <v>0</v>
@@ -20569,46 +20569,46 @@
         <v>2</v>
       </c>
       <c r="O205" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P205" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q205" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="R205" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="R205" s="2" t="n">
-        <v>19</v>
-      </c>
       <c r="S205" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T205" s="2" t="n">
         <v>3</v>
       </c>
       <c r="U205" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V205" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="W205" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="X205" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Y205" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z205" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA205" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB205" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -20637,28 +20637,28 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H206" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L206" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M206" s="2" t="n">
         <v>0</v>
@@ -20667,46 +20667,46 @@
         <v>2</v>
       </c>
       <c r="O206" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P206" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q206" s="2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="R206" s="2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="S206" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T206" s="2" t="n">
         <v>3</v>
       </c>
       <c r="U206" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V206" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W206" s="2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="X206" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y206" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z206" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA206" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB206" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -22293,32 +22293,32 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H223" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K223" s="2" t="n">
         <v>2</v>
@@ -22327,52 +22327,52 @@
         <v>1</v>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N223" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O223" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P223" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q223" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R223" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S223" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T223" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U223" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V223" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W223" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X223" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Y223" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z223" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA223" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB223" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -22391,32 +22391,32 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:15</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H224" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K224" s="2" t="n">
         <v>2</v>
@@ -22425,52 +22425,52 @@
         <v>1</v>
       </c>
       <c r="M224" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N224" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O224" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P224" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q224" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="R224" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S224" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T224" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="T224" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="U224" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V224" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W224" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="X224" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Y224" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z224" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA224" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB224" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
@@ -22685,35 +22685,35 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>01:07</t>
+          <t>03:15</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="H227" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I227" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J227" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K227" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L227" s="2" t="n">
         <v>0</v>
@@ -22722,49 +22722,49 @@
         <v>0</v>
       </c>
       <c r="N227" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O227" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P227" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q227" s="2" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="R227" s="2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="S227" s="2" t="n">
         <v>5</v>
       </c>
       <c r="T227" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U227" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="V227" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W227" s="2" t="n">
         <v>13</v>
       </c>
       <c r="X227" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y227" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z227" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA227" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB227" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -22783,35 +22783,35 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>01:07</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="H228" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I228" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K228" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L228" s="2" t="n">
         <v>0</v>
@@ -22820,49 +22820,49 @@
         <v>0</v>
       </c>
       <c r="N228" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O228" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P228" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q228" s="2" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="R228" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="S228" s="2" t="n">
         <v>5</v>
       </c>
       <c r="T228" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U228" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="V228" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W228" s="2" t="n">
         <v>13</v>
       </c>
       <c r="X228" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y228" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z228" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA228" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB228" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -22881,80 +22881,80 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>01:15</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="H229" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J229" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K229" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L229" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N229" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O229" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P229" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q229" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R229" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="S229" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T229" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U229" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V229" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="O229" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P229" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q229" s="2" t="n">
+      <c r="W229" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="R229" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="S229" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="T229" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="U229" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V229" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="W229" s="2" t="n">
-        <v>20</v>
-      </c>
       <c r="X229" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y229" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z229" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA229" s="2" t="n">
         <v>0</v>
@@ -22979,80 +22979,80 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H230" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K230" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L230" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M230" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N230" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O230" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P230" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q230" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="R230" s="2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="S230" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T230" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U230" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V230" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="W230" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="X230" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="W230" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="X230" s="2" t="n">
-        <v>9</v>
-      </c>
       <c r="Y230" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z230" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA230" s="2" t="n">
         <v>0</v>

--- a/datos/bbdd_ligamx.xlsx
+++ b/datos/bbdd_ligamx.xlsx
@@ -831,77 +831,77 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
         <v>13</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="S4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="T4" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="U4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W4" s="2" t="n">
         <v>9</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z4" s="2" t="n">
         <v>1</v>
@@ -929,77 +929,77 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q5" s="2" t="n">
         <v>13</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W5" s="2" t="n">
         <v>9</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>1</v>
@@ -1125,29 +1125,29 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>
@@ -1156,55 +1156,55 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="U7" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="V7" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W7" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="X7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y7" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1223,32 +1223,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>01:07</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -1260,46 +1260,46 @@
         <v>1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W8" s="2" t="n">
         <v>14</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" s="2" t="n">
         <v>0</v>
@@ -1321,29 +1321,29 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>0</v>
@@ -1352,55 +1352,55 @@
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W9" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X9" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="U9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="W9" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="X9" s="2" t="n">
-        <v>13</v>
-      </c>
       <c r="Y9" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1419,32 +1419,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>01:07</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -1456,46 +1456,46 @@
         <v>1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q10" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="R10" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="T10" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W10" s="2" t="n">
         <v>14</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="2" t="n">
         <v>0</v>
@@ -2203,86 +2203,86 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P18" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W18" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Y18" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Z18" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -2301,86 +2301,86 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P19" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="R19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="S19" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="T19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="V19" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="W19" s="2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="X19" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y19" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Z19" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2889,35 +2889,35 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>1</v>
@@ -2926,49 +2926,49 @@
         <v>1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U25" s="2" t="n">
         <v>6</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="W25" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="X25" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="Y25" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z25" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -2987,35 +2987,35 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>1</v>
@@ -3024,49 +3024,49 @@
         <v>1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U26" s="2" t="n">
         <v>6</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="W26" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Y26" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z26" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -3281,83 +3281,83 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="R29" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="S29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T29" s="2" t="n">
+      <c r="V29" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="U29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V29" s="2" t="n">
-        <v>16</v>
-      </c>
       <c r="W29" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="X29" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Y29" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Z29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" s="2" t="n">
         <v>0</v>
@@ -3477,83 +3477,83 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Atlante</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R31" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="W31" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X31" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="S31" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="T31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U31" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="V31" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="W31" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="X31" s="2" t="n">
-        <v>7</v>
-      </c>
       <c r="Y31" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Z31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB31" s="2" t="n">
         <v>0</v>
@@ -3575,86 +3575,86 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P32" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W32" s="2" t="n">
         <v>13</v>
       </c>
       <c r="X32" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y32" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Z32" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3673,29 +3673,29 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>01:10</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0</v>
@@ -3707,52 +3707,52 @@
         <v>0</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R33" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="S33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="V33" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="W33" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="X33" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Z33" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3771,86 +3771,86 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P34" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q34" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="R34" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="R34" s="2" t="n">
-        <v>14</v>
-      </c>
       <c r="S34" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V34" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="U34" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="V34" s="2" t="n">
-        <v>6</v>
       </c>
       <c r="W34" s="2" t="n">
         <v>13</v>
       </c>
       <c r="X34" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Y34" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Z34" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -3869,29 +3869,29 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>01:10</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0</v>
@@ -3903,52 +3903,52 @@
         <v>0</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="R35" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W35" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="S35" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U35" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="V35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W35" s="2" t="n">
+      <c r="X35" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="X35" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="Y35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Z35" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -3967,86 +3967,86 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:06</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O36" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="S36" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T36" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V36" s="2" t="n">
         <v>3</v>
       </c>
       <c r="W36" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X36" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="X36" s="2" t="n">
-        <v>14</v>
-      </c>
       <c r="Y36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -4065,86 +4065,86 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O37" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="R37" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="S37" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T37" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V37" s="2" t="n">
         <v>3</v>
       </c>
       <c r="W37" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="X37" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -4555,77 +4555,77 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I42" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q42" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R42" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="R42" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="S42" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T42" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V42" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W42" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y42" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z42" s="2" t="n">
         <v>1</v>
@@ -4653,77 +4653,77 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P43" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N43" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="O43" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P43" s="2" t="n">
+      <c r="Q43" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S43" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="Q43" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="R43" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="S43" s="2" t="n">
+      <c r="T43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V43" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W43" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X43" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="T43" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U43" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="V43" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W43" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="X43" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="Y43" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="2" t="n">
         <v>1</v>
@@ -5055,19 +5055,19 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Atlante</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0</v>
@@ -5076,55 +5076,55 @@
         <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R47" s="2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="S47" s="2" t="n">
         <v>4</v>
       </c>
       <c r="T47" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U47" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V47" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W47" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X47" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y47" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="U47" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V47" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="W47" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="X47" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y47" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="Z47" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -5143,86 +5143,86 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R48" s="2" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="S48" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T48" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U48" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V48" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W48" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="X48" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y48" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z48" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -5241,41 +5241,41 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" s="2" t="n">
         <v>0</v>
@@ -5287,37 +5287,37 @@
         <v>2</v>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R49" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S49" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T49" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U49" s="2" t="n">
         <v>3</v>
       </c>
       <c r="V49" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W49" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="X49" s="2" t="n">
         <v>10</v>
       </c>
       <c r="Y49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AA49" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB49" s="2" t="n">
         <v>1</v>
@@ -6025,80 +6025,80 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O57" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P57" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q57" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R57" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S57" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T57" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U57" s="2" t="n">
         <v>3</v>
       </c>
       <c r="V57" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W57" s="2" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="X57" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z57" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA57" s="2" t="n">
         <v>0</v>
@@ -6123,80 +6123,80 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N58" s="2" t="n">
         <v>2</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q58" s="2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="R58" s="2" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="S58" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T58" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U58" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V58" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W58" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="X58" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y58" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA58" s="2" t="n">
         <v>0</v>
@@ -6221,22 +6221,22 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Atlante</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
@@ -6252,49 +6252,49 @@
         <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P59" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q59" s="2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R59" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="S59" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T59" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U59" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V59" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W59" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="X59" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Y59" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z59" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA59" s="2" t="n">
         <v>0</v>
@@ -8279,32 +8279,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Mazatlan</t>
         </is>
       </c>
       <c r="H80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I80" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -8316,43 +8316,43 @@
         <v>1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O80" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P80" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q80" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S80" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="R80" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="S80" s="2" t="n">
-        <v>3</v>
       </c>
       <c r="T80" s="2" t="n">
         <v>6</v>
       </c>
       <c r="U80" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V80" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W80" s="2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="X80" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Y80" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z80" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA80" s="2" t="n">
         <v>0</v>
@@ -8377,80 +8377,80 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Mazatlan</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="H81" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N81" s="2" t="n">
         <v>2</v>
       </c>
       <c r="O81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P81" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q81" s="2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="R81" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="S81" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T81" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U81" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V81" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W81" s="2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="X81" s="2" t="n">
         <v>13</v>
       </c>
       <c r="Y81" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA81" s="2" t="n">
         <v>0</v>
@@ -8475,77 +8475,77 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P82" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q82" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R82" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="S82" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T82" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U82" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V82" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W82" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X82" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="V82" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W82" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="X82" s="2" t="n">
-        <v>13</v>
-      </c>
       <c r="Y82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z82" s="2" t="n">
         <v>0</v>
@@ -8573,35 +8573,35 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H83" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I83" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -8610,43 +8610,43 @@
         <v>1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P83" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q83" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="R83" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="R83" s="2" t="n">
-        <v>13</v>
-      </c>
       <c r="S83" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T83" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U83" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V83" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W83" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X83" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y83" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z83" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA83" s="2" t="n">
         <v>0</v>
@@ -8671,26 +8671,26 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>03:06</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I84" s="2" t="n">
         <v>1</v>
@@ -8699,7 +8699,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>1</v>
@@ -8711,46 +8711,46 @@
         <v>1</v>
       </c>
       <c r="O84" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P84" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q84" s="2" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="R84" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S84" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T84" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U84" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="V84" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W84" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X84" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y84" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z84" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="V84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W84" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="X84" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z84" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="AA84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -9063,26 +9063,26 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="H88" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I88" s="2" t="n">
         <v>1</v>
@@ -9091,7 +9091,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>1</v>
@@ -9103,46 +9103,46 @@
         <v>1</v>
       </c>
       <c r="O88" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P88" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q88" s="2" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="R88" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S88" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="T88" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U88" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W88" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X88" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y88" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z88" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T88" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U88" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="V88" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="W88" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="X88" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y88" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z88" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="AA88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -9455,32 +9455,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="H92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -9489,49 +9489,49 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P92" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q92" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R92" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S92" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T92" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U92" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V92" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W92" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X92" s="2" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="Y92" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z92" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB92" s="2" t="n">
         <v>0</v>
@@ -9651,32 +9651,32 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:06</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -9685,49 +9685,49 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q94" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R94" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S94" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T94" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U94" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V94" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W94" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X94" s="2" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="Y94" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z94" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB94" s="2" t="n">
         <v>0</v>
@@ -9749,80 +9749,80 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H95" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O95" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P95" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q95" s="2" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="R95" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="S95" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T95" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U95" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V95" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T95" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="U95" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="V95" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="W95" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X95" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y95" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z95" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA95" s="2" t="n">
         <v>0</v>
@@ -9945,80 +9945,80 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="H97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O97" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P97" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q97" s="2" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="R97" s="2" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="S97" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T97" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U97" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V97" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W97" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X97" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y97" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z97" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA97" s="2" t="n">
         <v>0</v>
@@ -10043,86 +10043,86 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:06</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H98" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O98" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P98" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q98" s="2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="R98" s="2" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="S98" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T98" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U98" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V98" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W98" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="X98" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y98" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z98" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -10239,86 +10239,86 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="H100" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O100" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P100" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="R100" s="2" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="S100" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T100" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U100" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V100" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="W100" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="X100" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y100" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z100" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -10337,77 +10337,77 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>01:10</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="H101" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O101" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P101" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q101" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S101" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T101" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U101" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V101" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W101" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="R101" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="S101" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="T101" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U101" s="2" t="n">
+      <c r="X101" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y101" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="V101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="X101" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y101" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="Z101" s="2" t="n">
         <v>2</v>
@@ -10435,86 +10435,86 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Mazatlan</t>
         </is>
       </c>
       <c r="H102" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O102" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P102" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q102" s="2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="R102" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="S102" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T102" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U102" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V102" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W102" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="X102" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="T102" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U102" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="V102" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="W102" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="X102" s="2" t="n">
-        <v>14</v>
-      </c>
       <c r="Y102" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z102" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -10533,86 +10533,86 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="H103" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O103" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P103" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q103" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="R103" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S103" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U103" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="Q103" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="R103" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="S103" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T103" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="U103" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="V103" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W103" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="X103" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y103" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Z103" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -10631,86 +10631,86 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Mazatlan</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="H104" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O104" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P104" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q104" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="R104" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="S104" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T104" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U104" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T104" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U104" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="V104" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W104" s="2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="X104" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Y104" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z104" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -10729,86 +10729,86 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>01:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H105" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O105" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P105" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q105" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R105" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S105" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T105" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U105" s="2" t="n">
         <v>6</v>
       </c>
       <c r="V105" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W105" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="X105" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y105" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z105" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB105" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -10935,76 +10935,76 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P107" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I107" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J107" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K107" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L107" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="O107" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P107" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="Q107" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R107" s="2" t="n">
         <v>8</v>
       </c>
       <c r="S107" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T107" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U107" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V107" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W107" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X107" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Y107" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z107" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -11023,83 +11023,83 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Mazatlan</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="H108" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M108" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O108" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P108" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q108" s="2" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="R108" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="S108" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T108" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U108" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V108" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W108" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X108" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y108" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z108" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB108" s="2" t="n">
         <v>0</v>
@@ -11131,67 +11131,67 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Mazatlan</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P109" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q109" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="R109" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="S109" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T109" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V109" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W109" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="S109" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T109" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U109" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V109" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="W109" s="2" t="n">
-        <v>16</v>
-      </c>
       <c r="X109" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y109" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z109" s="2" t="n">
         <v>2</v>
@@ -11219,86 +11219,86 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:06</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O110" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P110" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q110" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R110" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="S110" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T110" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U110" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V110" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="S110" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="T110" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U110" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V110" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="W110" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="X110" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="X110" s="2" t="n">
-        <v>17</v>
-      </c>
       <c r="Y110" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z110" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB110" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -11621,31 +11621,31 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H114" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N114" s="2" t="n">
         <v>1</v>
@@ -11657,40 +11657,40 @@
         <v>2</v>
       </c>
       <c r="Q114" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R114" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="S114" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T114" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T114" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="U114" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V114" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W114" s="2" t="n">
         <v>15</v>
       </c>
       <c r="X114" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Y114" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z114" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -11719,31 +11719,31 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H115" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N115" s="2" t="n">
         <v>1</v>
@@ -11755,40 +11755,40 @@
         <v>2</v>
       </c>
       <c r="Q115" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R115" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="S115" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T115" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U115" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="U115" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="V115" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="W115" s="2" t="n">
         <v>15</v>
       </c>
       <c r="X115" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Y115" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z115" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB115" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -12101,22 +12101,22 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>03:07</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H119" s="2" t="n">
@@ -12147,34 +12147,34 @@
         <v>1</v>
       </c>
       <c r="Q119" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R119" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S119" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T119" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U119" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="S119" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T119" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U119" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="V119" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W119" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X119" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="Y119" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z119" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA119" s="2" t="n">
         <v>0</v>
@@ -12199,29 +12199,29 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="H120" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>1</v>
@@ -12230,49 +12230,49 @@
         <v>0</v>
       </c>
       <c r="L120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P120" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q120" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R120" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S120" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T120" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U120" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V120" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W120" s="2" t="n">
         <v>17</v>
       </c>
       <c r="X120" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y120" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA120" s="2" t="n">
         <v>0</v>
@@ -12297,38 +12297,38 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="H121" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" s="2" t="n">
         <v>1</v>
@@ -12337,28 +12337,28 @@
         <v>2</v>
       </c>
       <c r="O121" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P121" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q121" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="R121" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S121" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T121" s="2" t="n">
         <v>4</v>
       </c>
       <c r="U121" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V121" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W121" s="2" t="n">
         <v>17</v>
@@ -12367,7 +12367,7 @@
         <v>10</v>
       </c>
       <c r="Y121" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z121" s="2" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
         <v>0</v>
       </c>
       <c r="AB121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -12395,86 +12395,86 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:07</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H122" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O122" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P122" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q122" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="R122" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="S122" s="2" t="n">
         <v>4</v>
       </c>
       <c r="T122" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U122" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V122" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W122" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="X122" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="W122" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="X122" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="Y122" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z122" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA122" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -12689,83 +12689,83 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="H125" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L125" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M125" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N125" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O125" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P125" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q125" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="R125" s="2" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="S125" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T125" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U125" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V125" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W125" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="U125" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V125" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="W125" s="2" t="n">
-        <v>13</v>
-      </c>
       <c r="X125" s="2" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="Y125" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z125" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA125" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB125" s="2" t="n">
         <v>0</v>
@@ -12787,83 +12787,83 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:06</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N126" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O126" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q126" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="R126" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="S126" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T126" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U126" s="2" t="n">
         <v>3</v>
       </c>
       <c r="V126" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W126" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="X126" s="2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="Y126" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB126" s="2" t="n">
         <v>0</v>
@@ -13865,83 +13865,83 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="H137" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J137" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L137" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O137" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P137" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q137" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R137" s="2" t="n">
         <v>11</v>
       </c>
       <c r="S137" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T137" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U137" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V137" s="2" t="n">
         <v>5</v>
       </c>
       <c r="W137" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X137" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y137" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z137" s="2" t="n">
         <v>4</v>
       </c>
       <c r="AA137" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB137" s="2" t="n">
         <v>0</v>
@@ -13963,83 +13963,83 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="H138" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M138" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P138" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q138" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="R138" s="2" t="n">
         <v>10</v>
       </c>
       <c r="S138" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T138" s="2" t="n">
         <v>4</v>
       </c>
       <c r="U138" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V138" s="2" t="n">
         <v>4</v>
       </c>
       <c r="W138" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X138" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y138" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z138" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB138" s="2" t="n">
         <v>0</v>
@@ -14061,77 +14061,77 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H139" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K139" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L139" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O139" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P139" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q139" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R139" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S139" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T139" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U139" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V139" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W139" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="X139" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y139" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z139" s="2" t="n">
         <v>3</v>
@@ -14159,83 +14159,83 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H140" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L140" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N140" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O140" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P140" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q140" s="2" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="R140" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S140" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T140" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="T140" s="2" t="n">
-        <v>4</v>
       </c>
       <c r="U140" s="2" t="n">
         <v>9</v>
       </c>
       <c r="V140" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W140" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="X140" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z140" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA140" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB140" s="2" t="n">
         <v>0</v>
@@ -14257,83 +14257,83 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="H141" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J141" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L141" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O141" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P141" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q141" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R141" s="2" t="n">
         <v>11</v>
       </c>
       <c r="S141" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T141" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U141" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V141" s="2" t="n">
         <v>5</v>
       </c>
       <c r="W141" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="X141" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Y141" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z141" s="2" t="n">
         <v>4</v>
       </c>
       <c r="AA141" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB141" s="2" t="n">
         <v>0</v>
@@ -15335,83 +15335,83 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="H152" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J152" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L152" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N152" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O152" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P152" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q152" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="R152" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="S152" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U152" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="U152" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="V152" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W152" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="X152" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Y152" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z152" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA152" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB152" s="2" t="n">
         <v>0</v>
@@ -15433,35 +15433,35 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H153" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I153" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L153" s="2" t="n">
         <v>0</v>
@@ -15470,40 +15470,40 @@
         <v>0</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O153" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P153" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q153" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="R153" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="S153" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="T153" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U153" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V153" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W153" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X153" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Y153" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z153" s="2" t="n">
         <v>2</v>
@@ -15512,7 +15512,7 @@
         <v>0</v>
       </c>
       <c r="AB153" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -15541,76 +15541,76 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H154" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J154" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L154" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M154" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O154" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P154" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q154" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="R154" s="2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="S154" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="T154" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U154" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V154" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W154" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="X154" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y154" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Z154" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA154" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB154" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -15629,22 +15629,22 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H155" s="2" t="n">
@@ -15660,55 +15660,55 @@
         <v>0</v>
       </c>
       <c r="L155" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O155" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P155" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q155" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R155" s="2" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="S155" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T155" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U155" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V155" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="U155" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="V155" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="W155" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="X155" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y155" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z155" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA155" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB155" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -15727,86 +15727,86 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="H156" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L156" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M156" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O156" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P156" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q156" s="2" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="R156" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S156" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T156" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U156" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V156" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W156" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="S156" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T156" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U156" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V156" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="W156" s="2" t="n">
-        <v>18</v>
-      </c>
       <c r="X156" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y156" s="2" t="n">
         <v>4</v>
       </c>
       <c r="Z156" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA156" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB156" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -16217,83 +16217,83 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="H161" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J161" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L161" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M161" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O161" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P161" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q161" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R161" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="R161" s="2" t="n">
-        <v>25</v>
-      </c>
       <c r="S161" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T161" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U161" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="U161" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="V161" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W161" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X161" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y161" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z161" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA161" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB161" s="2" t="n">
         <v>0</v>
@@ -16315,65 +16315,65 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H162" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L162" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O162" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P162" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q162" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R162" s="2" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="S162" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T162" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U162" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V162" s="2" t="n">
         <v>5</v>
@@ -16382,16 +16382,16 @@
         <v>11</v>
       </c>
       <c r="X162" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y162" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z162" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA162" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB162" s="2" t="n">
         <v>0</v>
@@ -16413,80 +16413,80 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="H163" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L163" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M163" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O163" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P163" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q163" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="R163" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="S163" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T163" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U163" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V163" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W163" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X163" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y163" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z163" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA163" s="2" t="n">
         <v>0</v>
@@ -16609,77 +16609,77 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="H165" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L165" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M165" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O165" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P165" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q165" s="2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="R165" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S165" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T165" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U165" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V165" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W165" s="2" t="n">
         <v>12</v>
       </c>
       <c r="X165" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y165" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z165" s="2" t="n">
         <v>3</v>
@@ -16707,35 +16707,35 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Mazatlan</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="H166" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I166" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L166" s="2" t="n">
         <v>0</v>
@@ -16744,43 +16744,43 @@
         <v>0</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O166" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P166" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q166" s="2" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="R166" s="2" t="n">
         <v>8</v>
       </c>
       <c r="S166" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T166" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U166" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V166" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W166" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X166" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Y166" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z166" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA166" s="2" t="n">
         <v>0</v>
@@ -16805,35 +16805,35 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Mazatlan</t>
         </is>
       </c>
       <c r="H167" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I167" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L167" s="2" t="n">
         <v>0</v>
@@ -16842,43 +16842,43 @@
         <v>0</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O167" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P167" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q167" s="2" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="R167" s="2" t="n">
         <v>8</v>
       </c>
       <c r="S167" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T167" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U167" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V167" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W167" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X167" s="2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Y167" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z167" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA167" s="2" t="n">
         <v>0</v>
@@ -17197,80 +17197,80 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H171" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L171" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O171" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P171" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q171" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="R171" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="S171" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="R171" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="S171" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="T171" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U171" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="U171" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="V171" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W171" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="X171" s="2" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Y171" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z171" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA171" s="2" t="n">
         <v>0</v>
@@ -17295,83 +17295,83 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H172" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J172" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L172" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O172" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P172" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q172" s="2" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="R172" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S172" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T172" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U172" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V172" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W172" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X172" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="T172" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U172" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="V172" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W172" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="X172" s="2" t="n">
-        <v>16</v>
-      </c>
       <c r="Y172" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z172" s="2" t="n">
         <v>3</v>
       </c>
       <c r="AA172" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB172" s="2" t="n">
         <v>0</v>
@@ -17393,26 +17393,26 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="H173" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I173" s="2" t="n">
         <v>0</v>
@@ -17421,7 +17421,7 @@
         <v>0</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L173" s="2" t="n">
         <v>0</v>
@@ -17433,43 +17433,43 @@
         <v>0</v>
       </c>
       <c r="O173" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P173" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q173" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="R173" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S173" s="2" t="n">
         <v>3</v>
       </c>
       <c r="T173" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U173" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V173" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W173" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="X173" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y173" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z173" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA173" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB173" s="2" t="n">
         <v>0</v>
@@ -17491,77 +17491,77 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H174" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K174" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L174" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M174" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O174" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P174" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q174" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="R174" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="S174" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T174" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U174" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V174" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W174" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="X174" s="2" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="Y174" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z174" s="2" t="n">
         <v>2</v>
@@ -18177,22 +18177,22 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="H181" s="2" t="n">
@@ -18208,55 +18208,55 @@
         <v>0</v>
       </c>
       <c r="L181" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O181" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P181" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q181" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R181" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S181" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T181" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U181" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V181" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W181" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="U181" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="V181" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="W181" s="2" t="n">
-        <v>9</v>
-      </c>
       <c r="X181" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Y181" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z181" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA181" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB181" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -18275,32 +18275,32 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="H182" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K182" s="2" t="n">
         <v>1</v>
@@ -18309,52 +18309,52 @@
         <v>0</v>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O182" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P182" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q182" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R182" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S182" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T182" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U182" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V182" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W182" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X182" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="R182" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="S182" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T182" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U182" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V182" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W182" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="X182" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="Y182" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z182" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA182" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB182" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -18373,32 +18373,32 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H183" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K183" s="2" t="n">
         <v>1</v>
@@ -18407,52 +18407,52 @@
         <v>0</v>
       </c>
       <c r="M183" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O183" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P183" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q183" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="R183" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="S183" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T183" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U183" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V183" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W183" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="R183" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="S183" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="T183" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U183" s="2" t="n">
+      <c r="X183" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="V183" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="W183" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="X183" s="2" t="n">
-        <v>9</v>
-      </c>
       <c r="Y183" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z183" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA183" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB183" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -18471,22 +18471,22 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H184" s="2" t="n">
@@ -18502,55 +18502,55 @@
         <v>0</v>
       </c>
       <c r="L184" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O184" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P184" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q184" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R184" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S184" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T184" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T184" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="U184" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V184" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="W184" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X184" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="V184" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W184" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="X184" s="2" t="n">
-        <v>12</v>
-      </c>
       <c r="Y184" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z184" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA184" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB184" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -19069,76 +19069,76 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="H190" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K190" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L190" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M190" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O190" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P190" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q190" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R190" s="2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="S190" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T190" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U190" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V190" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W190" s="2" t="n">
         <v>15</v>
       </c>
       <c r="X190" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Y190" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z190" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA190" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB190" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -19157,68 +19157,68 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:05</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H191" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I191" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K191" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L191" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N191" s="2" t="n">
         <v>2</v>
       </c>
       <c r="O191" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P191" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q191" s="2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="R191" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="S191" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T191" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U191" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="S191" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="T191" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U191" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="V191" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W191" s="2" t="n">
         <v>9</v>
@@ -19227,16 +19227,16 @@
         <v>10</v>
       </c>
       <c r="Y191" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z191" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA191" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB191" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -19255,35 +19255,35 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>03:05</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H192" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I192" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K192" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L192" s="2" t="n">
         <v>1</v>
@@ -19292,43 +19292,43 @@
         <v>0</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O192" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P192" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q192" s="2" t="n">
         <v>11</v>
       </c>
       <c r="R192" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="S192" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T192" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U192" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V192" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W192" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="X192" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y192" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z192" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA192" s="2" t="n">
         <v>0</v>
@@ -19353,71 +19353,71 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="H193" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K193" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L193" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M193" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O193" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P193" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q193" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="R193" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="S193" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T193" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="Q193" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="R193" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="S193" s="2" t="n">
+      <c r="U193" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T193" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="U193" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="V193" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W193" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X193" s="2" t="n">
         <v>13</v>
@@ -19426,7 +19426,7 @@
         <v>3</v>
       </c>
       <c r="Z193" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA193" s="2" t="n">
         <v>0</v>
@@ -19451,60 +19451,60 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="H194" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J194" s="2" t="n">
         <v>2</v>
       </c>
       <c r="K194" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L194" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M194" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O194" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P194" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q194" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R194" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S194" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Q194" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="R194" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="S194" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="T194" s="2" t="n">
         <v>1</v>
       </c>
@@ -19512,16 +19512,16 @@
         <v>4</v>
       </c>
       <c r="V194" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W194" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="X194" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y194" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z194" s="2" t="n">
         <v>2</v>
@@ -19530,7 +19530,7 @@
         <v>0</v>
       </c>
       <c r="AB194" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
@@ -20637,28 +20637,28 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="H206" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L206" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M206" s="2" t="n">
         <v>0</v>
@@ -20667,46 +20667,46 @@
         <v>2</v>
       </c>
       <c r="O206" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P206" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q206" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="R206" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="R206" s="2" t="n">
-        <v>19</v>
-      </c>
       <c r="S206" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T206" s="2" t="n">
         <v>3</v>
       </c>
       <c r="U206" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V206" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="W206" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="X206" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Y206" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z206" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA206" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB206" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
@@ -20735,28 +20735,28 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H207" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K207" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L207" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M207" s="2" t="n">
         <v>0</v>
@@ -20765,46 +20765,46 @@
         <v>2</v>
       </c>
       <c r="O207" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P207" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q207" s="2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="R207" s="2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="S207" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T207" s="2" t="n">
         <v>3</v>
       </c>
       <c r="U207" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V207" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W207" s="2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="X207" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y207" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z207" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA207" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB207" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -22783,35 +22783,35 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>01:07</t>
+          <t>03:15</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="H228" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I228" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K228" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L228" s="2" t="n">
         <v>0</v>
@@ -22820,49 +22820,49 @@
         <v>0</v>
       </c>
       <c r="N228" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O228" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P228" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q228" s="2" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="R228" s="2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="S228" s="2" t="n">
         <v>5</v>
       </c>
       <c r="T228" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U228" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="V228" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W228" s="2" t="n">
         <v>13</v>
       </c>
       <c r="X228" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y228" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z228" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA228" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB228" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -22881,35 +22881,35 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>01:07</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="H229" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I229" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J229" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K229" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L229" s="2" t="n">
         <v>0</v>
@@ -22918,49 +22918,49 @@
         <v>0</v>
       </c>
       <c r="N229" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O229" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P229" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q229" s="2" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="R229" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="S229" s="2" t="n">
         <v>5</v>
       </c>
       <c r="T229" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U229" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="V229" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W229" s="2" t="n">
         <v>13</v>
       </c>
       <c r="X229" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y229" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z229" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA229" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB229" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
@@ -22979,80 +22979,80 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>01:15</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="H230" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K230" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L230" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N230" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O230" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P230" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q230" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R230" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="S230" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T230" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U230" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V230" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="O230" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P230" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q230" s="2" t="n">
+      <c r="W230" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="R230" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="S230" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="T230" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="U230" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V230" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="W230" s="2" t="n">
-        <v>20</v>
-      </c>
       <c r="X230" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y230" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z230" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA230" s="2" t="n">
         <v>0</v>
@@ -23077,80 +23077,80 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H231" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K231" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L231" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M231" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N231" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O231" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P231" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q231" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="R231" s="2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="S231" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T231" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U231" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V231" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="W231" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="X231" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="W231" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="X231" s="2" t="n">
-        <v>9</v>
-      </c>
       <c r="Y231" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z231" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA231" s="2" t="n">
         <v>0</v>

--- a/datos/bbdd_ligamx.xlsx
+++ b/datos/bbdd_ligamx.xlsx
@@ -635,32 +635,32 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Atlante</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>2</v>
@@ -672,49 +672,49 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W2" s="2" t="n">
         <v>11</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -733,32 +733,32 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>2</v>
@@ -770,49 +770,49 @@
         <v>1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W3" s="2" t="n">
         <v>11</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1909,80 +1909,80 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W15" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="X15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="Y15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA15" s="2" t="n">
         <v>0</v>
@@ -2105,80 +2105,80 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T17" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="X17" s="2" t="n">
         <v>14</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA17" s="2" t="n">
         <v>0</v>
@@ -3379,77 +3379,77 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>01:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S30" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="O30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P30" s="2" t="n">
+      <c r="T30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V30" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="Q30" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="R30" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="S30" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="V30" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="W30" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X30" s="2" t="n">
         <v>7</v>
       </c>
       <c r="Y30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z30" s="2" t="n">
         <v>0</v>
@@ -3477,77 +3477,77 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:10</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Atlante</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="R31" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" s="2" t="n">
         <v>11</v>
-      </c>
-      <c r="S31" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="T31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U31" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="V31" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="W31" s="2" t="n">
-        <v>9</v>
       </c>
       <c r="X31" s="2" t="n">
         <v>7</v>
       </c>
       <c r="Y31" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="2" t="n">
         <v>0</v>
@@ -3575,35 +3575,35 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -3612,49 +3612,49 @@
         <v>0</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T32" s="2" t="n">
         <v>3</v>
       </c>
       <c r="U32" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X32" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="V32" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="W32" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="X32" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="Y32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z32" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3673,80 +3673,80 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>01:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S33" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V33" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="U33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="V33" s="2" t="n">
-        <v>7</v>
-      </c>
       <c r="W33" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="X33" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="X33" s="2" t="n">
-        <v>12</v>
-      </c>
       <c r="Y33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA33" s="2" t="n">
         <v>0</v>
@@ -3771,59 +3771,59 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:10</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T34" s="2" t="n">
         <v>5</v>
@@ -3832,25 +3832,25 @@
         <v>5</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W34" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="X34" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z34" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -3869,80 +3869,80 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q35" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="X35" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="R35" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="S35" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U35" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="V35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W35" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="X35" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="Y35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z35" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA35" s="2" t="n">
         <v>0</v>
@@ -5045,86 +5045,86 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R47" s="2" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="S47" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T47" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U47" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="V47" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W47" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X47" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Y47" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z47" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA47" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -5143,41 +5143,41 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Atlante</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" s="2" t="n">
         <v>0</v>
@@ -5189,37 +5189,37 @@
         <v>2</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="R48" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V48" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W48" s="2" t="n">
         <v>12</v>
-      </c>
-      <c r="S48" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T48" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U48" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V48" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="W48" s="2" t="n">
-        <v>19</v>
       </c>
       <c r="X48" s="2" t="n">
         <v>10</v>
       </c>
       <c r="Y48" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AA48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB48" s="2" t="n">
         <v>1</v>
@@ -5251,19 +5251,19 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0</v>
@@ -5272,55 +5272,55 @@
         <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P49" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="R49" s="2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="S49" s="2" t="n">
         <v>4</v>
       </c>
       <c r="T49" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U49" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V49" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W49" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="X49" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y49" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z49" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -7603,22 +7603,22 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -7630,40 +7630,40 @@
         <v>0</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R73" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="S73" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T73" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U73" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V73" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W73" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X73" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="Y73" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z73" s="2" t="n">
         <v>2</v>
@@ -7701,22 +7701,22 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -7728,40 +7728,40 @@
         <v>0</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q74" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R74" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="S74" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T74" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U74" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V74" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W74" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X74" s="2" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Y74" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z74" s="2" t="n">
         <v>2</v>
@@ -9357,74 +9357,74 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="H91" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I91" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N91" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O91" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P91" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q91" s="2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="R91" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S91" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T91" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U91" s="2" t="n">
         <v>7</v>
       </c>
       <c r="V91" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W91" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X91" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y91" s="2" t="n">
         <v>2</v>
@@ -9433,10 +9433,10 @@
         <v>3</v>
       </c>
       <c r="AA91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -9455,74 +9455,74 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="H92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I92" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N92" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P92" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q92" s="2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R92" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S92" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T92" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U92" s="2" t="n">
         <v>7</v>
       </c>
       <c r="V92" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W92" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X92" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y92" s="2" t="n">
         <v>2</v>
@@ -9531,10 +9531,10 @@
         <v>3</v>
       </c>
       <c r="AA92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -11229,67 +11229,67 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Mazatlan</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P110" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q110" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="R110" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="S110" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T110" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V110" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W110" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="S110" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T110" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U110" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V110" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="W110" s="2" t="n">
-        <v>16</v>
-      </c>
       <c r="X110" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y110" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z110" s="2" t="n">
         <v>2</v>
@@ -11327,67 +11327,67 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Mazatlan</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="H111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P111" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q111" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="R111" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S111" s="2" t="n">
         <v>3</v>
       </c>
       <c r="T111" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U111" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V111" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W111" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X111" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y111" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z111" s="2" t="n">
         <v>2</v>
@@ -12199,38 +12199,38 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="H120" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="n">
         <v>1</v>
@@ -12239,28 +12239,28 @@
         <v>2</v>
       </c>
       <c r="O120" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P120" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q120" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="R120" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S120" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="U120" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V120" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W120" s="2" t="n">
         <v>17</v>
@@ -12269,7 +12269,7 @@
         <v>10</v>
       </c>
       <c r="Y120" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z120" s="2" t="n">
         <v>0</v>
@@ -12278,7 +12278,7 @@
         <v>0</v>
       </c>
       <c r="AB120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -12297,86 +12297,86 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:07</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H121" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O121" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P121" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q121" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="R121" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="S121" s="2" t="n">
         <v>4</v>
       </c>
       <c r="T121" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U121" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V121" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W121" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="X121" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="W121" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="X121" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="Y121" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z121" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB121" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -12395,22 +12395,22 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>03:07</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H122" s="2" t="n">
@@ -12441,34 +12441,34 @@
         <v>1</v>
       </c>
       <c r="Q122" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R122" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S122" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T122" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U122" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="S122" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T122" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U122" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="V122" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W122" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X122" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="Y122" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z122" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA122" s="2" t="n">
         <v>0</v>
@@ -12493,29 +12493,29 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="H123" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>1</v>
@@ -12524,49 +12524,49 @@
         <v>0</v>
       </c>
       <c r="L123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P123" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q123" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R123" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S123" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T123" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U123" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V123" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W123" s="2" t="n">
         <v>17</v>
       </c>
       <c r="X123" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y123" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z123" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA123" s="2" t="n">
         <v>0</v>
@@ -12787,83 +12787,83 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="H126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N126" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O126" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q126" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="R126" s="2" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="S126" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T126" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U126" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V126" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W126" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="U126" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V126" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="W126" s="2" t="n">
-        <v>13</v>
-      </c>
       <c r="X126" s="2" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="Y126" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB126" s="2" t="n">
         <v>0</v>
@@ -12885,83 +12885,83 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:06</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H127" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N127" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O127" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P127" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q127" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="R127" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="S127" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T127" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U127" s="2" t="n">
         <v>3</v>
       </c>
       <c r="V127" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W127" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="X127" s="2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="Y127" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA127" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB127" s="2" t="n">
         <v>0</v>
@@ -13963,83 +13963,83 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="H138" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J138" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L138" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P138" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q138" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R138" s="2" t="n">
         <v>11</v>
       </c>
       <c r="S138" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T138" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U138" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V138" s="2" t="n">
         <v>5</v>
       </c>
       <c r="W138" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X138" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y138" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z138" s="2" t="n">
         <v>4</v>
       </c>
       <c r="AA138" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB138" s="2" t="n">
         <v>0</v>
@@ -14061,77 +14061,77 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H139" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K139" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L139" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O139" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P139" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q139" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R139" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S139" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T139" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U139" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V139" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W139" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="X139" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y139" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z139" s="2" t="n">
         <v>3</v>
@@ -14159,83 +14159,83 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H140" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L140" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N140" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O140" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P140" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q140" s="2" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="R140" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S140" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T140" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="T140" s="2" t="n">
-        <v>4</v>
       </c>
       <c r="U140" s="2" t="n">
         <v>9</v>
       </c>
       <c r="V140" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W140" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="X140" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z140" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA140" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB140" s="2" t="n">
         <v>0</v>
@@ -14257,83 +14257,83 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="H141" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L141" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M141" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O141" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P141" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q141" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="R141" s="2" t="n">
         <v>10</v>
       </c>
       <c r="S141" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T141" s="2" t="n">
         <v>4</v>
       </c>
       <c r="U141" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V141" s="2" t="n">
         <v>4</v>
       </c>
       <c r="W141" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X141" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y141" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z141" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA141" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB141" s="2" t="n">
         <v>0</v>
@@ -14355,83 +14355,83 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="H142" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J142" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O142" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P142" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q142" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R142" s="2" t="n">
         <v>11</v>
       </c>
       <c r="S142" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T142" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U142" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V142" s="2" t="n">
         <v>5</v>
       </c>
       <c r="W142" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="X142" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Y142" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z142" s="2" t="n">
         <v>4</v>
       </c>
       <c r="AA142" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB142" s="2" t="n">
         <v>0</v>
@@ -15443,76 +15443,76 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H153" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J153" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L153" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M153" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O153" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P153" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q153" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="R153" s="2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="S153" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="T153" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U153" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V153" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W153" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="X153" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y153" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Z153" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA153" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB153" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -15531,22 +15531,22 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H154" s="2" t="n">
@@ -15562,55 +15562,55 @@
         <v>0</v>
       </c>
       <c r="L154" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O154" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P154" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q154" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R154" s="2" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="S154" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U154" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V154" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="U154" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="V154" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="W154" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="X154" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y154" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z154" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA154" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB154" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -15629,86 +15629,86 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="H155" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L155" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O155" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P155" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q155" s="2" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="R155" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S155" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T155" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U155" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V155" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W155" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="S155" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T155" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U155" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V155" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="W155" s="2" t="n">
-        <v>18</v>
-      </c>
       <c r="X155" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y155" s="2" t="n">
         <v>4</v>
       </c>
       <c r="Z155" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA155" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB155" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -15727,83 +15727,83 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="H156" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J156" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L156" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N156" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O156" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P156" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q156" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="R156" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="S156" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="U156" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="V156" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W156" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="X156" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Y156" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z156" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA156" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB156" s="2" t="n">
         <v>0</v>
@@ -15825,35 +15825,35 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H157" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I157" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L157" s="2" t="n">
         <v>0</v>
@@ -15862,40 +15862,40 @@
         <v>0</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O157" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P157" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q157" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="R157" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="S157" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="T157" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U157" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V157" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W157" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X157" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Y157" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z157" s="2" t="n">
         <v>2</v>
@@ -15904,7 +15904,7 @@
         <v>0</v>
       </c>
       <c r="AB157" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -16315,38 +16315,38 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H162" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L162" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M162" s="2" t="n">
         <v>0</v>
@@ -16355,43 +16355,43 @@
         <v>2</v>
       </c>
       <c r="O162" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P162" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q162" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R162" s="2" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="S162" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T162" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U162" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V162" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W162" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X162" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y162" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z162" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA162" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB162" s="2" t="n">
         <v>0</v>
@@ -16413,77 +16413,77 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="H163" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L163" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M163" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O163" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P163" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q163" s="2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="R163" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S163" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T163" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U163" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V163" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W163" s="2" t="n">
         <v>12</v>
       </c>
       <c r="X163" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y163" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z163" s="2" t="n">
         <v>3</v>
@@ -16511,22 +16511,22 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="H164" s="2" t="n">
@@ -16536,10 +16536,10 @@
         <v>1</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L164" s="2" t="n">
         <v>0</v>
@@ -16548,43 +16548,43 @@
         <v>1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P164" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q164" s="2" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="R164" s="2" t="n">
         <v>12</v>
       </c>
       <c r="S164" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T164" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V164" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="U164" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="V164" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="W164" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X164" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y164" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z164" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA164" s="2" t="n">
         <v>0</v>
@@ -16609,22 +16609,22 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="H165" s="2" t="n">
@@ -16634,10 +16634,10 @@
         <v>1</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L165" s="2" t="n">
         <v>0</v>
@@ -16646,43 +16646,43 @@
         <v>1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O165" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P165" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q165" s="2" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="R165" s="2" t="n">
         <v>12</v>
       </c>
       <c r="S165" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T165" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U165" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V165" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W165" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X165" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y165" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z165" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA165" s="2" t="n">
         <v>0</v>
@@ -16707,83 +16707,83 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="H166" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J166" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L166" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M166" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O166" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P166" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q166" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R166" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="R166" s="2" t="n">
-        <v>25</v>
-      </c>
       <c r="S166" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T166" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U166" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="U166" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="V166" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W166" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X166" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y166" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z166" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA166" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB166" s="2" t="n">
         <v>0</v>
@@ -17295,26 +17295,26 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="H172" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I172" s="2" t="n">
         <v>0</v>
@@ -17323,7 +17323,7 @@
         <v>0</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L172" s="2" t="n">
         <v>0</v>
@@ -17335,43 +17335,43 @@
         <v>0</v>
       </c>
       <c r="O172" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P172" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q172" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="R172" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S172" s="2" t="n">
         <v>3</v>
       </c>
       <c r="T172" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U172" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V172" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W172" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="X172" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y172" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z172" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA172" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB172" s="2" t="n">
         <v>0</v>
@@ -17393,77 +17393,77 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H173" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K173" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L173" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M173" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O173" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P173" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q173" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="R173" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="S173" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T173" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U173" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V173" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W173" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="X173" s="2" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="Y173" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z173" s="2" t="n">
         <v>2</v>
@@ -17491,80 +17491,80 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H174" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L174" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O174" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P174" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q174" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="R174" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="S174" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="R174" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="S174" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="T174" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U174" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="U174" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="V174" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W174" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="X174" s="2" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Y174" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z174" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA174" s="2" t="n">
         <v>0</v>
@@ -17589,83 +17589,83 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H175" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J175" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L175" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M175" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O175" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P175" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q175" s="2" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="R175" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S175" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T175" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U175" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V175" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W175" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X175" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="T175" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U175" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="V175" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W175" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="X175" s="2" t="n">
-        <v>16</v>
-      </c>
       <c r="Y175" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z175" s="2" t="n">
         <v>3</v>
       </c>
       <c r="AA175" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB175" s="2" t="n">
         <v>0</v>
@@ -18275,86 +18275,86 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="H182" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J182" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L182" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M182" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N182" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O182" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P182" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q182" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R182" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="S182" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T182" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U182" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="V182" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W182" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X182" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="W182" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="X182" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="Y182" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Z182" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA182" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB182" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -18373,86 +18373,86 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="H183" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L183" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M183" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O183" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P183" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q183" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R183" s="2" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="S183" s="2" t="n">
         <v>6</v>
       </c>
       <c r="T183" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U183" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V183" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W183" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="X183" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="X183" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="Y183" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z183" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA183" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB183" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -18569,32 +18569,32 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="H185" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I185" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K185" s="2" t="n">
         <v>1</v>
@@ -18606,49 +18606,49 @@
         <v>0</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P185" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q185" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="R185" s="2" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="S185" s="2" t="n">
         <v>6</v>
       </c>
       <c r="T185" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U185" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V185" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W185" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X185" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y185" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z185" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA185" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB185" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -18667,22 +18667,22 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H186" s="2" t="n">
@@ -18698,55 +18698,55 @@
         <v>0</v>
       </c>
       <c r="L186" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O186" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P186" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q186" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R186" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S186" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T186" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T186" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="U186" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V186" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="W186" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X186" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="V186" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W186" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="X186" s="2" t="n">
-        <v>12</v>
-      </c>
       <c r="Y186" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z186" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA186" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB186" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -19647,86 +19647,86 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Mazatlan</t>
         </is>
       </c>
       <c r="H196" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I196" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K196" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L196" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M196" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O196" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P196" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q196" s="2" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="R196" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="S196" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="S196" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="T196" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U196" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V196" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W196" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="X196" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y196" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z196" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA196" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB196" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -19745,86 +19745,86 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Mazatlan</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H197" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I197" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K197" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L197" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M197" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O197" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P197" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q197" s="2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R197" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="S197" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T197" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U197" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="V197" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W197" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X197" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="W197" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="X197" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="Y197" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z197" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA197" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB197" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -19853,22 +19853,22 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>Mazatlan</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="H198" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K198" s="2" t="n">
         <v>0</v>
@@ -19877,46 +19877,46 @@
         <v>1</v>
       </c>
       <c r="M198" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O198" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P198" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q198" s="2" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="R198" s="2" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="S198" s="2" t="n">
         <v>3</v>
       </c>
       <c r="T198" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U198" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V198" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W198" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X198" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Y198" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z198" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA198" s="2" t="n">
         <v>0</v>
@@ -19951,22 +19951,22 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Mazatlan</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="H199" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K199" s="2" t="n">
         <v>0</v>
@@ -19975,46 +19975,46 @@
         <v>1</v>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O199" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P199" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q199" s="2" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="R199" s="2" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="S199" s="2" t="n">
         <v>3</v>
       </c>
       <c r="T199" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U199" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V199" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W199" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X199" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Y199" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z199" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA199" s="2" t="n">
         <v>0</v>
@@ -21705,83 +21705,83 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>Mazatlan</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H217" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I217" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J217" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K217" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L217" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M217" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O217" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P217" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I217" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J217" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K217" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L217" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M217" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N217" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O217" s="2" t="n">
+      <c r="Q217" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="R217" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S217" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T217" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="P217" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q217" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="R217" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="S217" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="T217" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="U217" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V217" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W217" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="X217" s="2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="Y217" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z217" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA217" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB217" s="2" t="n">
         <v>0</v>
@@ -21803,83 +21803,83 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>01:07</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="H218" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K218" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L218" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M218" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O218" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P218" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q218" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R218" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="S218" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T218" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U218" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V218" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W218" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="X218" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Y218" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z218" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA218" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB218" s="2" t="n">
         <v>0</v>
@@ -21901,77 +21901,77 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>01:07</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H219" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J219" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K219" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L219" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M219" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P219" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q219" s="2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="R219" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S219" s="2" t="n">
         <v>4</v>
       </c>
       <c r="T219" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U219" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V219" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W219" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X219" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y219" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z219" s="2" t="n">
         <v>1</v>
@@ -21999,80 +21999,80 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="H220" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I220" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K220" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L220" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M220" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O220" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P220" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q220" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="R220" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S220" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T220" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U220" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V220" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W220" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="X220" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="R220" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="S220" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T220" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U220" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="V220" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W220" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="X220" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="Y220" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z220" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA220" s="2" t="n">
         <v>0</v>
@@ -22097,29 +22097,29 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="H221" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J221" s="2" t="n">
         <v>0</v>
@@ -22128,52 +22128,52 @@
         <v>0</v>
       </c>
       <c r="L221" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O221" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P221" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q221" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="R221" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S221" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T221" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U221" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V221" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W221" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X221" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="S221" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T221" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U221" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="V221" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="W221" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="X221" s="2" t="n">
-        <v>12</v>
-      </c>
       <c r="Y221" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z221" s="2" t="n">
         <v>2</v>
       </c>
       <c r="AA221" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB221" s="2" t="n">
         <v>0</v>
@@ -22205,73 +22205,73 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Mazatlan</t>
         </is>
       </c>
       <c r="H222" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K222" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L222" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M222" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N222" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O222" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P222" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q222" s="2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="R222" s="2" t="n">
         <v>8</v>
       </c>
       <c r="S222" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T222" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U222" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V222" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W222" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="X222" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y222" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z222" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA222" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB222" s="2" t="n">
         <v>0</v>
@@ -22293,86 +22293,86 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="H223" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K223" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L223" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N223" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O223" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P223" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q223" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R223" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S223" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T223" s="2" t="n">
         <v>2</v>
       </c>
       <c r="U223" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V223" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W223" s="2" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="X223" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y223" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z223" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA223" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB223" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -22391,86 +22391,86 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="H224" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K224" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L224" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M224" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N224" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O224" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P224" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q224" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R224" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S224" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T224" s="2" t="n">
         <v>2</v>
       </c>
       <c r="U224" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V224" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W224" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="X224" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Y224" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z224" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA224" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB224" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225">
@@ -22685,83 +22685,83 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>01:15</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="H227" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J227" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K227" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L227" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M227" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N227" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O227" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P227" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q227" s="2" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="R227" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="S227" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T227" s="2" t="n">
         <v>6</v>
       </c>
       <c r="U227" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V227" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W227" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X227" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Y227" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Z227" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA227" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB227" s="2" t="n">
         <v>0</v>
@@ -22783,83 +22783,83 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="H228" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K228" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L228" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N228" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O228" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P228" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q228" s="2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="R228" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="S228" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T228" s="2" t="n">
         <v>6</v>
       </c>
       <c r="U228" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V228" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W228" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X228" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y228" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Z228" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA228" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB228" s="2" t="n">
         <v>0</v>
@@ -22881,35 +22881,35 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>01:07</t>
+          <t>03:15</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="H229" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I229" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J229" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K229" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L229" s="2" t="n">
         <v>0</v>
@@ -22918,49 +22918,49 @@
         <v>0</v>
       </c>
       <c r="N229" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O229" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P229" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q229" s="2" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="R229" s="2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="S229" s="2" t="n">
         <v>5</v>
       </c>
       <c r="T229" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U229" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="V229" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W229" s="2" t="n">
         <v>13</v>
       </c>
       <c r="X229" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y229" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z229" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA229" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB229" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -22979,35 +22979,35 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>01:07</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="H230" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I230" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K230" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L230" s="2" t="n">
         <v>0</v>
@@ -23016,49 +23016,49 @@
         <v>0</v>
       </c>
       <c r="N230" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O230" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P230" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q230" s="2" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="R230" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="S230" s="2" t="n">
         <v>5</v>
       </c>
       <c r="T230" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U230" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="V230" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W230" s="2" t="n">
         <v>13</v>
       </c>
       <c r="X230" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y230" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z230" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA230" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB230" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -23077,80 +23077,80 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>01:15</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="H231" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K231" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L231" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N231" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O231" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P231" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q231" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R231" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="S231" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T231" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U231" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V231" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="O231" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P231" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q231" s="2" t="n">
+      <c r="W231" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="R231" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="S231" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="T231" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="U231" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V231" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="W231" s="2" t="n">
-        <v>20</v>
-      </c>
       <c r="X231" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y231" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z231" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA231" s="2" t="n">
         <v>0</v>
@@ -23175,80 +23175,80 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H232" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J232" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K232" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L232" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M232" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N232" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O232" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P232" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q232" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="R232" s="2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="S232" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T232" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U232" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V232" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="W232" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="X232" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="W232" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="X232" s="2" t="n">
-        <v>9</v>
-      </c>
       <c r="Y232" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z232" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA232" s="2" t="n">
         <v>0</v>
@@ -24203,7 +24203,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>237 partidos (Apertura 2026: 70 partidos, Clausura 2026: 167 partidos). 28 columnas. Cargado el 16/09/2026.</t>
+          <t>237 partidos (Apertura 2026: 70 partidos, Clausura 2026: 167 partidos). 28 columnas. Cargado el 17/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_ligamx.xlsx
+++ b/datos/bbdd_ligamx.xlsx
@@ -635,32 +635,32 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>2</v>
@@ -672,49 +672,49 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W2" s="2" t="n">
         <v>11</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -733,32 +733,32 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Atlante</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>2</v>
@@ -770,49 +770,49 @@
         <v>1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W3" s="2" t="n">
         <v>11</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1909,80 +1909,80 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W15" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="X15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="Y15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA15" s="2" t="n">
         <v>0</v>
@@ -2105,80 +2105,80 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T17" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="X17" s="2" t="n">
         <v>14</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA17" s="2" t="n">
         <v>0</v>
@@ -3379,77 +3379,77 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:10</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Atlante</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="R30" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" s="2" t="n">
         <v>11</v>
-      </c>
-      <c r="S30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="T30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U30" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="V30" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="W30" s="2" t="n">
-        <v>9</v>
       </c>
       <c r="X30" s="2" t="n">
         <v>7</v>
       </c>
       <c r="Y30" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="2" t="n">
         <v>0</v>
@@ -3477,77 +3477,77 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>01:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S31" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="O31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P31" s="2" t="n">
+      <c r="T31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V31" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="Q31" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="R31" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="S31" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U31" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="V31" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="W31" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X31" s="2" t="n">
         <v>7</v>
       </c>
       <c r="Y31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z31" s="2" t="n">
         <v>0</v>
@@ -3575,80 +3575,80 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q32" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="X32" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="R32" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="S32" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T32" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U32" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="V32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W32" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="X32" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="Y32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z32" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA32" s="2" t="n">
         <v>0</v>
@@ -3673,35 +3673,35 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -3710,49 +3710,49 @@
         <v>0</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="S33" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T33" s="2" t="n">
         <v>3</v>
       </c>
       <c r="U33" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X33" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="V33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="W33" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="X33" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="Y33" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z33" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3771,80 +3771,80 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>01:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V34" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="U34" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="V34" s="2" t="n">
-        <v>7</v>
-      </c>
       <c r="W34" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="X34" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="X34" s="2" t="n">
-        <v>12</v>
-      </c>
       <c r="Y34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA34" s="2" t="n">
         <v>0</v>
@@ -3869,59 +3869,59 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:10</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S35" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T35" s="2" t="n">
         <v>5</v>
@@ -3930,25 +3930,25 @@
         <v>5</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W35" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="X35" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z35" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -5055,19 +5055,19 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0</v>
@@ -5076,55 +5076,55 @@
         <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="R47" s="2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="S47" s="2" t="n">
         <v>4</v>
       </c>
       <c r="T47" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U47" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V47" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W47" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="X47" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y47" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z47" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -5143,86 +5143,86 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R48" s="2" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="S48" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T48" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U48" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="V48" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W48" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X48" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Y48" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA48" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -5241,41 +5241,41 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Atlante</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" s="2" t="n">
         <v>0</v>
@@ -5287,37 +5287,37 @@
         <v>2</v>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="R49" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W49" s="2" t="n">
         <v>12</v>
-      </c>
-      <c r="S49" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T49" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U49" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V49" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="W49" s="2" t="n">
-        <v>19</v>
       </c>
       <c r="X49" s="2" t="n">
         <v>10</v>
       </c>
       <c r="Y49" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AA49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB49" s="2" t="n">
         <v>1</v>
@@ -7603,22 +7603,22 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -7630,40 +7630,40 @@
         <v>0</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q73" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R73" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="S73" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T73" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U73" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V73" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W73" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X73" s="2" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Y73" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z73" s="2" t="n">
         <v>2</v>
@@ -7701,22 +7701,22 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="H74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -7728,40 +7728,40 @@
         <v>0</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q74" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R74" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="S74" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T74" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U74" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V74" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W74" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X74" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="Y74" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z74" s="2" t="n">
         <v>2</v>
@@ -9357,74 +9357,74 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="H91" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I91" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N91" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O91" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P91" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q91" s="2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R91" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S91" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T91" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U91" s="2" t="n">
         <v>7</v>
       </c>
       <c r="V91" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W91" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X91" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y91" s="2" t="n">
         <v>2</v>
@@ -9433,10 +9433,10 @@
         <v>3</v>
       </c>
       <c r="AA91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -9455,74 +9455,74 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="H92" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I92" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N92" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O92" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P92" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q92" s="2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="R92" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S92" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T92" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U92" s="2" t="n">
         <v>7</v>
       </c>
       <c r="V92" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W92" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X92" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y92" s="2" t="n">
         <v>2</v>
@@ -9531,10 +9531,10 @@
         <v>3</v>
       </c>
       <c r="AA92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -11229,67 +11229,67 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Mazatlan</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P110" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q110" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="R110" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S110" s="2" t="n">
         <v>3</v>
       </c>
       <c r="T110" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U110" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V110" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W110" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X110" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y110" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z110" s="2" t="n">
         <v>2</v>
@@ -11327,67 +11327,67 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Mazatlan</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P111" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q111" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="R111" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="S111" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T111" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V111" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W111" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="S111" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T111" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U111" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V111" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="W111" s="2" t="n">
-        <v>16</v>
-      </c>
       <c r="X111" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y111" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z111" s="2" t="n">
         <v>2</v>
@@ -12199,86 +12199,86 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:07</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H120" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O120" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P120" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q120" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="R120" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="S120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="T120" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U120" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V120" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W120" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="X120" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="W120" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="X120" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="Y120" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z120" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA120" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -12297,22 +12297,22 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>03:07</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H121" s="2" t="n">
@@ -12343,34 +12343,34 @@
         <v>1</v>
       </c>
       <c r="Q121" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R121" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S121" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T121" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U121" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="S121" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T121" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U121" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="V121" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W121" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X121" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="Y121" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z121" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA121" s="2" t="n">
         <v>0</v>
@@ -12395,29 +12395,29 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="H122" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>1</v>
@@ -12426,49 +12426,49 @@
         <v>0</v>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P122" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q122" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R122" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S122" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T122" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U122" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V122" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W122" s="2" t="n">
         <v>17</v>
       </c>
       <c r="X122" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y122" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA122" s="2" t="n">
         <v>0</v>
@@ -12493,38 +12493,38 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="H123" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="n">
         <v>1</v>
@@ -12533,28 +12533,28 @@
         <v>2</v>
       </c>
       <c r="O123" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P123" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q123" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="R123" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S123" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T123" s="2" t="n">
         <v>4</v>
       </c>
       <c r="U123" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V123" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W123" s="2" t="n">
         <v>17</v>
@@ -12563,7 +12563,7 @@
         <v>10</v>
       </c>
       <c r="Y123" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z123" s="2" t="n">
         <v>0</v>
@@ -12572,7 +12572,7 @@
         <v>0</v>
       </c>
       <c r="AB123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -12787,83 +12787,83 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>03:06</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N126" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O126" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q126" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="R126" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="S126" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T126" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U126" s="2" t="n">
         <v>3</v>
       </c>
       <c r="V126" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W126" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="X126" s="2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="Y126" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB126" s="2" t="n">
         <v>0</v>
@@ -12885,83 +12885,83 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="H127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M127" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N127" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O127" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P127" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q127" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="R127" s="2" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="S127" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T127" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U127" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V127" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W127" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="U127" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V127" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="W127" s="2" t="n">
-        <v>13</v>
-      </c>
       <c r="X127" s="2" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="Y127" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z127" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB127" s="2" t="n">
         <v>0</v>
@@ -13963,83 +13963,83 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="H138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J138" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L138" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P138" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q138" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R138" s="2" t="n">
         <v>11</v>
       </c>
       <c r="S138" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T138" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U138" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V138" s="2" t="n">
         <v>5</v>
       </c>
       <c r="W138" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="X138" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Y138" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z138" s="2" t="n">
         <v>4</v>
       </c>
       <c r="AA138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB138" s="2" t="n">
         <v>0</v>
@@ -14061,83 +14061,83 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="H139" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L139" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M139" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O139" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P139" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q139" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="R139" s="2" t="n">
         <v>10</v>
       </c>
       <c r="S139" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T139" s="2" t="n">
         <v>4</v>
       </c>
       <c r="U139" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V139" s="2" t="n">
         <v>4</v>
       </c>
       <c r="W139" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X139" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y139" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z139" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA139" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB139" s="2" t="n">
         <v>0</v>
@@ -14159,77 +14159,77 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H140" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K140" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L140" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O140" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P140" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q140" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R140" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S140" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T140" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U140" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V140" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W140" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="X140" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y140" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z140" s="2" t="n">
         <v>3</v>
@@ -14257,83 +14257,83 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H141" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J141" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L141" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M141" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N141" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O141" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P141" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q141" s="2" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="R141" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S141" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T141" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="T141" s="2" t="n">
-        <v>4</v>
       </c>
       <c r="U141" s="2" t="n">
         <v>9</v>
       </c>
       <c r="V141" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W141" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="X141" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y141" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z141" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA141" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB141" s="2" t="n">
         <v>0</v>
@@ -14355,83 +14355,83 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="H142" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J142" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L142" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O142" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P142" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q142" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R142" s="2" t="n">
         <v>11</v>
       </c>
       <c r="S142" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T142" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U142" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V142" s="2" t="n">
         <v>5</v>
       </c>
       <c r="W142" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X142" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y142" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z142" s="2" t="n">
         <v>4</v>
       </c>
       <c r="AA142" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB142" s="2" t="n">
         <v>0</v>
@@ -15433,22 +15433,22 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H153" s="2" t="n">
@@ -15464,55 +15464,55 @@
         <v>0</v>
       </c>
       <c r="L153" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O153" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P153" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q153" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R153" s="2" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="S153" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T153" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U153" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V153" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="U153" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="V153" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="W153" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="X153" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y153" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z153" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA153" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB153" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -15531,86 +15531,86 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>01:06</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="H154" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L154" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O154" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P154" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q154" s="2" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="R154" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T154" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U154" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W154" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="S154" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T154" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U154" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V154" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="W154" s="2" t="n">
-        <v>18</v>
-      </c>
       <c r="X154" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y154" s="2" t="n">
         <v>4</v>
       </c>
       <c r="Z154" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA154" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB154" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -15629,83 +15629,83 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="H155" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J155" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L155" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N155" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O155" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P155" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q155" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="R155" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="S155" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="U155" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="V155" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W155" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="X155" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Y155" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z155" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA155" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB155" s="2" t="n">
         <v>0</v>
@@ -15727,35 +15727,35 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H156" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I156" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L156" s="2" t="n">
         <v>0</v>
@@ -15764,40 +15764,40 @@
         <v>0</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O156" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P156" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q156" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="R156" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="S156" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="T156" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U156" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V156" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W156" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X156" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Y156" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z156" s="2" t="n">
         <v>2</v>
@@ -15806,7 +15806,7 @@
         <v>0</v>
       </c>
       <c r="AB156" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -15835,76 +15835,76 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H157" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J157" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L157" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M157" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O157" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P157" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q157" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="R157" s="2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="S157" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="T157" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U157" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V157" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W157" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="X157" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y157" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Z157" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA157" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB157" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -16315,83 +16315,83 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="H162" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J162" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L162" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M162" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O162" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P162" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q162" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R162" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="R162" s="2" t="n">
-        <v>25</v>
-      </c>
       <c r="S162" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T162" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U162" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="U162" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="V162" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W162" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X162" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y162" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z162" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA162" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB162" s="2" t="n">
         <v>0</v>
@@ -16413,38 +16413,38 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="H163" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L163" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M163" s="2" t="n">
         <v>0</v>
@@ -16453,43 +16453,43 @@
         <v>2</v>
       </c>
       <c r="O163" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P163" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q163" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R163" s="2" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="S163" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T163" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U163" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V163" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W163" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X163" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y163" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z163" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA163" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB163" s="2" t="n">
         <v>0</v>
@@ -16511,22 +16511,22 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="H164" s="2" t="n">
@@ -16536,10 +16536,10 @@
         <v>1</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L164" s="2" t="n">
         <v>0</v>
@@ -16548,43 +16548,43 @@
         <v>1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P164" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q164" s="2" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="R164" s="2" t="n">
         <v>12</v>
       </c>
       <c r="S164" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T164" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U164" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V164" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W164" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X164" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y164" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z164" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA164" s="2" t="n">
         <v>0</v>
@@ -16609,22 +16609,22 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="H165" s="2" t="n">
@@ -16634,10 +16634,10 @@
         <v>1</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L165" s="2" t="n">
         <v>0</v>
@@ -16646,43 +16646,43 @@
         <v>1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O165" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P165" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q165" s="2" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="R165" s="2" t="n">
         <v>12</v>
       </c>
       <c r="S165" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T165" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V165" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="U165" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="V165" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="W165" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X165" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y165" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z165" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA165" s="2" t="n">
         <v>0</v>
@@ -16707,77 +16707,77 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="H166" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L166" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M166" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O166" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P166" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q166" s="2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="R166" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S166" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T166" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U166" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V166" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W166" s="2" t="n">
         <v>12</v>
       </c>
       <c r="X166" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y166" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z166" s="2" t="n">
         <v>3</v>
@@ -17295,77 +17295,77 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H172" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K172" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L172" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M172" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O172" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P172" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q172" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="R172" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="S172" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T172" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U172" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V172" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W172" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="X172" s="2" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="Y172" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z172" s="2" t="n">
         <v>2</v>
@@ -17393,80 +17393,80 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H173" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L173" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O173" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P173" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q173" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="R173" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="S173" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="R173" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="S173" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="T173" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U173" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="U173" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="V173" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W173" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="X173" s="2" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Y173" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z173" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA173" s="2" t="n">
         <v>0</v>
@@ -17491,83 +17491,83 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H174" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J174" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L174" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O174" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P174" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q174" s="2" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="R174" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S174" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T174" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U174" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V174" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W174" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X174" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="T174" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U174" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="V174" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W174" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="X174" s="2" t="n">
-        <v>16</v>
-      </c>
       <c r="Y174" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z174" s="2" t="n">
         <v>3</v>
       </c>
       <c r="AA174" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB174" s="2" t="n">
         <v>0</v>
@@ -17589,26 +17589,26 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="H175" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I175" s="2" t="n">
         <v>0</v>
@@ -17617,7 +17617,7 @@
         <v>0</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L175" s="2" t="n">
         <v>0</v>
@@ -17629,43 +17629,43 @@
         <v>0</v>
       </c>
       <c r="O175" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P175" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q175" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="R175" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S175" s="2" t="n">
         <v>3</v>
       </c>
       <c r="T175" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U175" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V175" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W175" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="X175" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y175" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z175" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA175" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB175" s="2" t="n">
         <v>0</v>
@@ -18275,32 +18275,32 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="H182" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I182" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K182" s="2" t="n">
         <v>1</v>
@@ -18312,49 +18312,49 @@
         <v>0</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O182" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P182" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q182" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="R182" s="2" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="S182" s="2" t="n">
         <v>6</v>
       </c>
       <c r="T182" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U182" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V182" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W182" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X182" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y182" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z182" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA182" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB182" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -18373,22 +18373,22 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H183" s="2" t="n">
@@ -18404,55 +18404,55 @@
         <v>0</v>
       </c>
       <c r="L183" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O183" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P183" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q183" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R183" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S183" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T183" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T183" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="U183" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V183" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="W183" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X183" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="V183" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W183" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="X183" s="2" t="n">
-        <v>12</v>
-      </c>
       <c r="Y183" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z183" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA183" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB183" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -18569,86 +18569,86 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="H185" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K185" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L185" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M185" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P185" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q185" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R185" s="2" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="S185" s="2" t="n">
         <v>6</v>
       </c>
       <c r="T185" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U185" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V185" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W185" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="X185" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="X185" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="Y185" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z185" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA185" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB185" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -18667,86 +18667,86 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="H186" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J186" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K186" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L186" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N186" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O186" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P186" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q186" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R186" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="S186" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T186" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U186" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="V186" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W186" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X186" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="W186" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="X186" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="Y186" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Z186" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA186" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB186" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -19647,86 +19647,86 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Mazatlan</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H196" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I196" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K196" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L196" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M196" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O196" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P196" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q196" s="2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R196" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="S196" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T196" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U196" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="V196" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W196" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X196" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="W196" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="X196" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="Y196" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z196" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA196" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB196" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -19745,86 +19745,86 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Mazatlan</t>
         </is>
       </c>
       <c r="H197" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I197" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K197" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L197" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O197" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P197" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q197" s="2" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="R197" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="S197" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="S197" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="T197" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U197" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V197" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W197" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="X197" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y197" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z197" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA197" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB197" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -19853,22 +19853,22 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Mazatlan</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="H198" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K198" s="2" t="n">
         <v>0</v>
@@ -19877,46 +19877,46 @@
         <v>1</v>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O198" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P198" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q198" s="2" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="R198" s="2" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="S198" s="2" t="n">
         <v>3</v>
       </c>
       <c r="T198" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U198" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V198" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W198" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X198" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Y198" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z198" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA198" s="2" t="n">
         <v>0</v>
@@ -19951,22 +19951,22 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>Mazatlan</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="H199" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K199" s="2" t="n">
         <v>0</v>
@@ -19975,46 +19975,46 @@
         <v>1</v>
       </c>
       <c r="M199" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O199" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P199" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q199" s="2" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="R199" s="2" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="S199" s="2" t="n">
         <v>3</v>
       </c>
       <c r="T199" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U199" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V199" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W199" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X199" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Y199" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z199" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA199" s="2" t="n">
         <v>0</v>
@@ -21705,83 +21705,83 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>01:07</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="H217" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K217" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L217" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M217" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O217" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P217" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q217" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R217" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="S217" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T217" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U217" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V217" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W217" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="X217" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Y217" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z217" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA217" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB217" s="2" t="n">
         <v>0</v>
@@ -21803,77 +21803,77 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>01:07</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="H218" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K218" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L218" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M218" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O218" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P218" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q218" s="2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="R218" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S218" s="2" t="n">
         <v>4</v>
       </c>
       <c r="T218" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U218" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V218" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W218" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X218" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y218" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z218" s="2" t="n">
         <v>1</v>
@@ -21901,80 +21901,80 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="H219" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I219" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J219" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K219" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L219" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M219" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O219" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P219" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q219" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="R219" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S219" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T219" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U219" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V219" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W219" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="X219" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="R219" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="S219" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T219" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U219" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="V219" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W219" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="X219" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="Y219" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z219" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA219" s="2" t="n">
         <v>0</v>
@@ -21999,29 +21999,29 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="H220" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J220" s="2" t="n">
         <v>0</v>
@@ -22030,52 +22030,52 @@
         <v>0</v>
       </c>
       <c r="L220" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M220" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O220" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P220" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q220" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="R220" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S220" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T220" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U220" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V220" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W220" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X220" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="S220" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T220" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U220" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="V220" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="W220" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="X220" s="2" t="n">
-        <v>12</v>
-      </c>
       <c r="Y220" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z220" s="2" t="n">
         <v>2</v>
       </c>
       <c r="AA220" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB220" s="2" t="n">
         <v>0</v>
@@ -22107,73 +22107,73 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Mazatlan</t>
         </is>
       </c>
       <c r="H221" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K221" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L221" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M221" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O221" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P221" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q221" s="2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="R221" s="2" t="n">
         <v>8</v>
       </c>
       <c r="S221" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T221" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U221" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V221" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W221" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="X221" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y221" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z221" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA221" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB221" s="2" t="n">
         <v>0</v>
@@ -22195,83 +22195,83 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>Mazatlan</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="H222" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I222" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J222" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K222" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L222" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O222" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P222" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I222" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J222" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K222" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L222" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M222" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N222" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O222" s="2" t="n">
+      <c r="Q222" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="R222" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S222" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T222" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="P222" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q222" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="R222" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="S222" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="T222" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="U222" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V222" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W222" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="X222" s="2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="Y222" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z222" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA222" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB222" s="2" t="n">
         <v>0</v>
@@ -22293,86 +22293,86 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="H223" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K223" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L223" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M223" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N223" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O223" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P223" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q223" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R223" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S223" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T223" s="2" t="n">
         <v>2</v>
       </c>
       <c r="U223" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V223" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W223" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="X223" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Y223" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z223" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA223" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB223" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224">
@@ -22391,86 +22391,86 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="H224" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K224" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L224" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N224" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O224" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P224" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q224" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R224" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S224" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T224" s="2" t="n">
         <v>2</v>
       </c>
       <c r="U224" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V224" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W224" s="2" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="X224" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y224" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z224" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA224" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB224" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -22685,83 +22685,83 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="H227" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J227" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K227" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L227" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N227" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O227" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P227" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q227" s="2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="R227" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="S227" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T227" s="2" t="n">
         <v>6</v>
       </c>
       <c r="U227" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V227" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W227" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X227" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y227" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Z227" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA227" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB227" s="2" t="n">
         <v>0</v>
@@ -22783,83 +22783,83 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>01:15</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>America</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="H228" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K228" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L228" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M228" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N228" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O228" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P228" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q228" s="2" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="R228" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="S228" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T228" s="2" t="n">
         <v>6</v>
       </c>
       <c r="U228" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V228" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W228" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X228" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Y228" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Z228" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA228" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB228" s="2" t="n">
         <v>0</v>
@@ -22881,35 +22881,35 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>01:07</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="H229" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I229" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J229" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K229" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L229" s="2" t="n">
         <v>0</v>
@@ -22918,49 +22918,49 @@
         <v>0</v>
       </c>
       <c r="N229" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O229" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P229" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q229" s="2" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="R229" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="S229" s="2" t="n">
         <v>5</v>
       </c>
       <c r="T229" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U229" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="V229" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W229" s="2" t="n">
         <v>13</v>
       </c>
       <c r="X229" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y229" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z229" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA229" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB229" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
@@ -22979,35 +22979,35 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>01:07</t>
+          <t>03:15</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="H230" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I230" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K230" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L230" s="2" t="n">
         <v>0</v>
@@ -23016,49 +23016,49 @@
         <v>0</v>
       </c>
       <c r="N230" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O230" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P230" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q230" s="2" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="R230" s="2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="S230" s="2" t="n">
         <v>5</v>
       </c>
       <c r="T230" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U230" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="V230" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W230" s="2" t="n">
         <v>13</v>
       </c>
       <c r="X230" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y230" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z230" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA230" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AB230" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -23077,80 +23077,80 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>America</t>
         </is>
       </c>
       <c r="H231" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K231" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L231" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M231" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N231" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O231" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P231" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q231" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="R231" s="2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="S231" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T231" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U231" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V231" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="W231" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="X231" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="W231" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="X231" s="2" t="n">
-        <v>9</v>
-      </c>
       <c r="Y231" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z231" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA231" s="2" t="n">
         <v>0</v>
@@ -23175,80 +23175,80 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>01:15</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="H232" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J232" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K232" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L232" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N232" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O232" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P232" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q232" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R232" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="S232" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T232" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U232" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V232" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="O232" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P232" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q232" s="2" t="n">
+      <c r="W232" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="R232" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="S232" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="T232" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="U232" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V232" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="W232" s="2" t="n">
-        <v>20</v>
-      </c>
       <c r="X232" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y232" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z232" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA232" s="2" t="n">
         <v>0</v>
@@ -24203,7 +24203,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>237 partidos (Apertura 2026: 70 partidos, Clausura 2026: 167 partidos). 28 columnas. Cargado el 17/09/2026.</t>
+          <t>237 partidos (Apertura 2026: 70 partidos, Clausura 2026: 167 partidos). 28 columnas. Cargado el 18/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
